--- a/预算/装修需求与预算_20261006.xlsx
+++ b/预算/装修需求与预算_20261006.xlsx
@@ -15,14 +15,14 @@
     <sheet name="依据与实测" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">确认需求!$A$5:$D$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">预算明细!$A$5:$J$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">依据与实测!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">报价对照!$A$1:$I$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">确认需求!$A$1:$D$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">确认需求!$A$5:$D$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">预算明细!$A$5:$J$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">依据与实测!$A$1:$D$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">报价对照!$A$1:$I$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">确认需求!$A$1:$D$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">采购节奏!$A$1:$D$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">预算总览!$A$1:$E$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">预算明细!$A$1:$J$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">预算明细!$A$1:$J$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">依据与实测!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">报价对照!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">确认需求!$1:$5</definedName>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="391">
   <si>
     <t>装修需求与预算</t>
   </si>
@@ -283,7 +283,7 @@
     <t>设备</t>
   </si>
   <si>
-    <t>两台台式机、共三块显示器，一个双屏工位，一个单屏工位。</t>
+    <t>两台台式机，各一块显示器，共两块屏幕；替代之前的双屏＋单屏设想。</t>
   </si>
   <si>
     <t>采购口径</t>
@@ -298,10 +298,10 @@
     <t>位置</t>
   </si>
   <si>
-    <t>用户提出放客厅可能更宽敞；优先评估客厅，但尚未最终定位置。</t>
-  </si>
-  <si>
-    <t>待布局复核</t>
+    <t>用户希望靠近客厅窗户；本版沿靠阳台的两侧墙各放120×60cm桌，中间留通路。</t>
+  </si>
+  <si>
+    <t>靠窗偏好已确认；占位待复尺</t>
   </si>
   <si>
     <t>客厅</t>
@@ -313,6 +313,33 @@
     <t>保留沙发、电视位置，未来会买Switch等主机；不因工位取消娱乐区。</t>
   </si>
   <si>
+    <t>餐桌</t>
+  </si>
+  <si>
+    <t>希望饭桌可收纳；本版采用带抽屉折叠桌，收拢30×80cm、展开120×80cm。</t>
+  </si>
+  <si>
+    <t>收纳要求已确认；尺寸为建议</t>
+  </si>
+  <si>
+    <t>床朝向</t>
+  </si>
+  <si>
+    <t>用户希望床调个面；本版先把床头换到图面右侧墙，可切回左侧比较。</t>
+  </si>
+  <si>
+    <t>用户要求调整；具体朝向为方案解释</t>
+  </si>
+  <si>
+    <t>新增顶柜</t>
+  </si>
+  <si>
+    <t>用户希望考虑上方打柜；工位、电视墙、主卧门洞及次卧柜顶先排备选模块。</t>
+  </si>
+  <si>
+    <t>需求已记录；柜量与固定条件待复尺</t>
+  </si>
+  <si>
     <t>厨房</t>
   </si>
   <si>
@@ -469,10 +496,10 @@
     <t>水电重做及未来设备预留</t>
   </si>
   <si>
-    <t>按新布局重做；双人工位插座与网口，空调点位，洗烘机、洗碗机、机器人接口，电动窗帘电源。</t>
-  </si>
-  <si>
-    <t>列点位图、回路、水管电线品牌规格及计价方式；此项含管线底盒，面板在灯具面板项核算。</t>
+    <t>按新布局重做；靠阳台两侧单屏工位的插座网口，空调点位，洗烘机、洗碗机、机器人接口，电动窗帘电源。</t>
+  </si>
+  <si>
+    <t>列点位图、回路、水管电线品牌规格及计价方式；窗边桌线缆走墙，避开窗帘和阳台门。此项含管线底盒，面板另核算。</t>
   </si>
   <si>
     <t>防水、找平及基层修复</t>
@@ -541,10 +568,10 @@
     <t>主卧及基础收纳</t>
   </si>
   <si>
-    <t>主卧顶柜＋挂衣杆＋帘子，鞋柜及少量储物；先按两人日常衣物量规划。</t>
-  </si>
-  <si>
-    <t>列柜体展开/投影计价方式、板材型号、五金、固定方式；梳妆台在家具项。</t>
+    <t>原需求主卧顶柜＋挂衣杆＋帘子，鞋柜及基础储物；先按两人日常衣物量规划。新增浅顶柜另列备选。</t>
+  </si>
+  <si>
+    <t>列柜体计价方式、板材五金、墙体固定；梳妆台在家具项。主卧原顶柜已计此行，不能在新增顶柜中重复报价。</t>
   </si>
   <si>
     <t>外窗全部换新</t>
@@ -607,7 +634,7 @@
     <t>助手建议宽1.8米，床长优先2.1米；窄边床架；两人188cm/100kg与160cm/50kg。</t>
   </si>
   <si>
-    <t>此为方案建议，完整床架尺寸、床垫试躺及承重需复核；2.1米长款如需定制应明确价格。</t>
+    <t>本版先按床头左右对调、靠图面右侧墙；完整床架尺寸、试躺与承重需复核；2.1米长款如需定制应明确价格。</t>
   </si>
   <si>
     <t>客厅沙发</t>
@@ -622,19 +649,19 @@
     <t>餐桌椅</t>
   </si>
   <si>
-    <t>两人日常使用，暂按紧凑2～4座成品套装。</t>
-  </si>
-  <si>
-    <t>尺寸及座位数为预算假设，结合客餐厅工位最终布局选购。</t>
+    <t>用户希望可收纳；本版按带抽屉折叠餐桌＋两把可折叠椅，收拢约30×80cm、展开约120×80cm。</t>
+  </si>
+  <si>
+    <t>尺寸为占位建议，实际产品需核对稳定性、桌翼支撑、折叠椅是否能收入；展开前将桌子移出墙边。</t>
   </si>
   <si>
     <t>两张电脑桌</t>
   </si>
   <si>
-    <t>两台台式机、三块屏幕，一个双屏工位，一个单屏工位；双屏桌稍宽。</t>
-  </si>
-  <si>
-    <t>电脑硬件不计采购；工位位置尚未最终确定，优先评估客厅可用墙面。</t>
+    <t>两台台式机各一块屏幕；本版两张120×60cm桌，放在客厅靠阳台窗的两侧墙边。</t>
+  </si>
+  <si>
+    <t>电脑硬件不计采购；核对显示器与主机外尺寸。按58cm椅子收近桌边时中间约82cm，需实测已有椅子与阳台门。</t>
   </si>
   <si>
     <t>补一把电脑椅</t>
@@ -808,6 +835,15 @@
     <t>未计当前合计；按窗帘数量、轨道长度、型号及安装核对。</t>
   </si>
   <si>
+    <t>新增浅顶柜（方案备选）</t>
+  </si>
+  <si>
+    <t>两个工位上方、电视墙上方、主卧门洞上方及次卧柜补顶层，共约5.48延米；前四处深30cm，次卧延续50cm深。</t>
+  </si>
+  <si>
+    <t>规划估算，未取得柜体报价；需按板材五金、墙体可靠固定、梁和门窗空调净空复尺。主卧原顶柜已计基础收纳，勿重复。</t>
+  </si>
+  <si>
     <t>计入项目合计</t>
   </si>
   <si>
@@ -832,7 +868,7 @@
     <t>方案及询价</t>
   </si>
   <si>
-    <t>确定双人工位与沙发电视餐区的整体布局；复尺床、橱柜、门窗和洗衣区。</t>
+    <t>复尺窗边两侧单屏工位、折叠餐桌、沙发电视区、床调向、浅顶柜、门窗与洗衣区。</t>
   </si>
   <si>
     <t>设备购买可延后，但冰箱、洗烘机、洗碗机、机器人等拟选型号的外尺寸与安装条件需先确定。</t>
@@ -895,7 +931,7 @@
     <t>按需升级</t>
   </si>
   <si>
-    <t>次卧空调、净水器、智能锁升级、电动窗帘电机和轨道。</t>
+    <t>次卧空调、净水器、智能锁、电动窗帘；新增浅顶柜先确定是否随硬装做。</t>
   </si>
   <si>
     <t>这些是备选，当前合计未包含；确认购买再把“计入”改为1。</t>
@@ -946,6 +982,12 @@
     <t>未填写全部必需范围前，合计只是已填金额；未报价/漏项不等于免费。</t>
   </si>
   <si>
+    <t>备选：新增浅顶柜</t>
+  </si>
+  <si>
+    <t>单独报新增五处柜体价格，原主卧顶柜扣重；本行不计入上方同口径必需报价合计。</t>
+  </si>
+  <si>
     <t>资料依据与现场待核</t>
   </si>
   <si>
@@ -1075,13 +1117,37 @@
     <t>客餐厅工位布局</t>
   </si>
   <si>
-    <t>客餐厅含餐区，双人工位尚未定；须保留沙发电视与游戏主机位置，测连续墙面、门窗、椅子活动和通道。</t>
-  </si>
-  <si>
-    <t>待平面布置复核</t>
-  </si>
-  <si>
-    <t>两台台式机，一个双屏工位一个单屏工位。</t>
+    <t>两台台式机各一屏；桌子靠阳台两侧墙，中间约82cm通路以58cm椅子收近为前提。餐桌折叠并移出展开。</t>
+  </si>
+  <si>
+    <t>2026-10-06第2版；待复尺</t>
+  </si>
+  <si>
+    <t>屏幕侧对窗，窗帘控制反光；测实际椅子、窗帘、门洞、线缆和主机。</t>
+  </si>
+  <si>
+    <t>窗边工位采光</t>
+  </si>
+  <si>
+    <t>屏幕与窗面尽量成直角，配窗帘调节反光；采用侧向来光的排布。</t>
+  </si>
+  <si>
+    <t>官方工位环境建议</t>
+  </si>
+  <si>
+    <t>https://www.osha.gov/etools/computer-workstations/workstation-environment</t>
+  </si>
+  <si>
+    <t>新增顶柜固定</t>
+  </si>
+  <si>
+    <t>柜底先按2.2m、顶2.65m；主卧门洞、工位和电视墙用30cm深浅柜，次卧柜补顶层；不只依靠装饰吊顶承重。</t>
+  </si>
+  <si>
+    <t>板材与墙体待现场核对</t>
+  </si>
+  <si>
+    <t>https://www.ikea.com.cy/files/Homepage/Howtobuyyourkitchen/ENHET_installation_guide_cy_en.pdf</t>
   </si>
   <si>
     <t>主卧布局</t>
@@ -1093,7 +1159,7 @@
     <t>待实测与试躺</t>
   </si>
   <si>
-    <t>主卧可比较不同朝向摆放；床长并非已由用户最终下单确定。</t>
+    <t>本版默认床头靠图面右侧墙，180×210cm床垫的窄边床架脚边约63cm；可切回原朝向或比较200cm床长。</t>
   </si>
   <si>
     <t>洗衣区与机器人</t>
@@ -1722,15 +1788,15 @@
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!B6:B44,A7,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A7,预算明细!I6:I45,1)</f>
         <v>53100</v>
       </c>
       <c r="C7" s="6">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!B6:B44,A7,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A7,预算明细!I6:I45,1)</f>
         <v>79000</v>
       </c>
       <c r="D7" s="6">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!B6:B44,A7,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A7,预算明细!I6:I45,1)</f>
         <v>65200</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -1742,15 +1808,15 @@
         <v>10</v>
       </c>
       <c r="B8" s="6">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!B6:B44,A8,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A8,预算明细!I6:I45,1)</f>
         <v>10100</v>
       </c>
       <c r="C8" s="6">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!B6:B44,A8,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A8,预算明细!I6:I45,1)</f>
         <v>17500</v>
       </c>
       <c r="D8" s="6">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!B6:B44,A8,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A8,预算明细!I6:I45,1)</f>
         <v>13000</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -1762,15 +1828,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="6">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!B6:B44,A9,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A9,预算明细!I6:I45,1)</f>
         <v>3800</v>
       </c>
       <c r="C9" s="6">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!B6:B44,A9,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A9,预算明细!I6:I45,1)</f>
         <v>7000</v>
       </c>
       <c r="D9" s="6">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!B6:B44,A9,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A9,预算明细!I6:I45,1)</f>
         <v>5200</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -1782,15 +1848,15 @@
         <v>14</v>
       </c>
       <c r="B10" s="6">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!B6:B44,A10,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A10,预算明细!I6:I45,1)</f>
         <v>9300</v>
       </c>
       <c r="C10" s="6">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!B6:B44,A10,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A10,预算明细!I6:I45,1)</f>
         <v>16500</v>
       </c>
       <c r="D10" s="6">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!B6:B44,A10,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A10,预算明细!I6:I45,1)</f>
         <v>12800</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -1802,15 +1868,15 @@
         <v>16</v>
       </c>
       <c r="B11" s="6">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!B6:B44,A11,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A11,预算明细!I6:I45,1)</f>
         <v>10300</v>
       </c>
       <c r="C11" s="6">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!B6:B44,A11,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A11,预算明细!I6:I45,1)</f>
         <v>15800</v>
       </c>
       <c r="D11" s="6">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!B6:B44,A11,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A11,预算明细!I6:I45,1)</f>
         <v>13100</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -1822,15 +1888,15 @@
         <v>18</v>
       </c>
       <c r="B12" s="6">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!B6:B44,A12,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A12,预算明细!I6:I45,1)</f>
         <v>8000</v>
       </c>
       <c r="C12" s="6">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!B6:B44,A12,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A12,预算明细!I6:I45,1)</f>
         <v>12500</v>
       </c>
       <c r="D12" s="6">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!B6:B44,A12,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A12,预算明细!I6:I45,1)</f>
         <v>9600</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -1842,15 +1908,15 @@
         <v>20</v>
       </c>
       <c r="B13" s="6">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!B6:B44,A13,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A13,预算明细!I6:I45,1)</f>
         <v>3500</v>
       </c>
       <c r="C13" s="6">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!B6:B44,A13,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A13,预算明细!I6:I45,1)</f>
         <v>5800</v>
       </c>
       <c r="D13" s="6">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!B6:B44,A13,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A13,预算明细!I6:I45,1)</f>
         <v>4400</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -1862,15 +1928,15 @@
         <v>22</v>
       </c>
       <c r="B14" s="6">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!B6:B44,A14,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A14,预算明细!I6:I45,1)</f>
         <v>0</v>
       </c>
       <c r="C14" s="6">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!B6:B44,A14,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A14,预算明细!I6:I45,1)</f>
         <v>0</v>
       </c>
       <c r="D14" s="6">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!B6:B44,A14,预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A14,预算明细!I6:I45,1)</f>
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -1882,15 +1948,15 @@
         <v>24</v>
       </c>
       <c r="B16" s="8">
-        <f>SUMIFS(预算明细!E6:E44,预算明细!H6:H44,"首批",预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!E6:E45,预算明细!H6:H45,"首批",预算明细!I6:I45,1)</f>
         <v>86600</v>
       </c>
       <c r="C16" s="8">
-        <f>SUMIFS(预算明细!F6:F44,预算明细!H6:H44,"首批",预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!F6:F45,预算明细!H6:H45,"首批",预算明细!I6:I45,1)</f>
         <v>135800</v>
       </c>
       <c r="D16" s="8">
-        <f>SUMIFS(预算明细!G6:G44,预算明细!H6:H44,"首批",预算明细!I6:I44,1)</f>
+        <f>SUMIFS(预算明细!G6:G45,预算明细!H6:H45,"首批",预算明细!I6:I45,1)</f>
         <v>109300</v>
       </c>
       <c r="E16" s="7" t="s">
@@ -1942,15 +2008,15 @@
         <v>30</v>
       </c>
       <c r="B20" s="8">
-        <f>SUMIF(预算明细!I6:I44,1,预算明细!E6:E44)-B16</f>
+        <f>SUMIF(预算明细!I6:I45,1,预算明细!E6:E45)-B16</f>
         <v>11500</v>
       </c>
       <c r="C20" s="8">
-        <f>SUMIF(预算明细!I6:I44,1,预算明细!F6:F44)-C16</f>
+        <f>SUMIF(预算明细!I6:I45,1,预算明细!F6:F45)-C16</f>
         <v>18300</v>
       </c>
       <c r="D20" s="8">
-        <f>SUMIF(预算明细!I6:I44,1,预算明细!G6:G44)-D16</f>
+        <f>SUMIF(预算明细!I6:I45,1,预算明细!G6:G45)-D16</f>
         <v>14000</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -2027,7 +2093,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="32" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -2328,21 +2394,21 @@
     </row>
     <row r="24" spans="1:4" ht="44" customHeight="1">
       <c r="A24" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="44" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>95</v>
@@ -2351,46 +2417,46 @@
         <v>96</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="44" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="44" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="44" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>47</v>
@@ -2398,7 +2464,7 @@
     </row>
     <row r="29" spans="1:4" ht="44" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>106</v>
@@ -2407,32 +2473,32 @@
         <v>107</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="44" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="44" customHeight="1">
       <c r="A31" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>47</v>
@@ -2440,30 +2506,30 @@
     </row>
     <row r="32" spans="1:4" ht="44" customHeight="1">
       <c r="A32" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="D32" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="44" customHeight="1">
       <c r="A33" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="44" customHeight="1">
@@ -2491,7 +2557,7 @@
         <v>126</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="44" customHeight="1">
@@ -2505,11 +2571,53 @@
         <v>129</v>
       </c>
       <c r="D36" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="44" customHeight="1">
+      <c r="A37" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="44" customHeight="1">
+      <c r="A38" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>76</v>
       </c>
     </row>
+    <row r="39" spans="1:4" ht="44" customHeight="1">
+      <c r="A39" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:D36"/>
+  <autoFilter ref="A5:D39"/>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -2529,7 +2637,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="32" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -2544,7 +2652,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2558,7 +2666,7 @@
     </row>
     <row r="2" spans="1:10" ht="34" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2572,7 +2680,7 @@
     </row>
     <row r="4" spans="1:10" ht="40" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2586,16 +2694,16 @@
     </row>
     <row r="5" spans="1:10" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>4</v>
@@ -2607,13 +2715,13 @@
         <v>6</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="78" customHeight="1">
@@ -2624,10 +2732,10 @@
         <v>8</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E6" s="6">
         <v>6000</v>
@@ -2639,13 +2747,13 @@
         <v>7500</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I6" s="10">
         <v>1</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="78" customHeight="1">
@@ -2656,10 +2764,10 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E7" s="6">
         <v>8000</v>
@@ -2671,13 +2779,13 @@
         <v>9500</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I7" s="10">
         <v>1</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="78" customHeight="1">
@@ -2688,10 +2796,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E8" s="6">
         <v>4500</v>
@@ -2703,13 +2811,13 @@
         <v>6000</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="78" customHeight="1">
@@ -2720,10 +2828,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E9" s="6">
         <v>11000</v>
@@ -2735,13 +2843,13 @@
         <v>13000</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I9" s="10">
         <v>1</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="78" customHeight="1">
@@ -2752,10 +2860,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E10" s="6">
         <v>5500</v>
@@ -2767,13 +2875,13 @@
         <v>6500</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I10" s="10">
         <v>1</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="78" customHeight="1">
@@ -2784,10 +2892,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E11" s="6">
         <v>1800</v>
@@ -2799,13 +2907,13 @@
         <v>2200</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I11" s="10">
         <v>1</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="78" customHeight="1">
@@ -2816,10 +2924,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E12" s="6">
         <v>3500</v>
@@ -2831,13 +2939,13 @@
         <v>4500</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I12" s="10">
         <v>1</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="78" customHeight="1">
@@ -2848,10 +2956,10 @@
         <v>8</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E13" s="6">
         <v>6500</v>
@@ -2863,13 +2971,13 @@
         <v>8000</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I13" s="10">
         <v>1</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="78" customHeight="1">
@@ -2880,10 +2988,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E14" s="6">
         <v>2800</v>
@@ -2895,13 +3003,13 @@
         <v>3500</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I14" s="10">
         <v>1</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="78" customHeight="1">
@@ -2912,10 +3020,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E15" s="6">
         <v>3500</v>
@@ -2927,13 +3035,13 @@
         <v>4500</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="78" customHeight="1">
@@ -2944,10 +3052,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E16" s="6">
         <v>7000</v>
@@ -2959,13 +3067,13 @@
         <v>9000</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I16" s="10">
         <v>1</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="78" customHeight="1">
@@ -2976,10 +3084,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E17" s="6">
         <v>2500</v>
@@ -2991,13 +3099,13 @@
         <v>3000</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I17" s="10">
         <v>1</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="78" customHeight="1">
@@ -3008,10 +3116,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E18" s="6">
         <v>600</v>
@@ -3023,13 +3131,13 @@
         <v>1000</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I18" s="10">
         <v>1</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="78" customHeight="1">
@@ -3040,10 +3148,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E19" s="6">
         <v>1800</v>
@@ -3055,13 +3163,13 @@
         <v>2400</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I19" s="10">
         <v>1</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="78" customHeight="1">
@@ -3072,10 +3180,10 @@
         <v>12</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="E20" s="6">
         <v>1200</v>
@@ -3087,13 +3195,13 @@
         <v>1600</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I20" s="10">
         <v>1</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="78" customHeight="1">
@@ -3104,10 +3212,10 @@
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="E21" s="6">
         <v>800</v>
@@ -3119,13 +3227,13 @@
         <v>1200</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I21" s="10">
         <v>1</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="78" customHeight="1">
@@ -3136,10 +3244,10 @@
         <v>14</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E22" s="6">
         <v>3500</v>
@@ -3151,13 +3259,13 @@
         <v>4500</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I22" s="10">
         <v>1</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="78" customHeight="1">
@@ -3168,10 +3276,10 @@
         <v>14</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="E23" s="6">
         <v>1800</v>
@@ -3183,13 +3291,13 @@
         <v>2500</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I23" s="10">
         <v>1</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="78" customHeight="1">
@@ -3200,10 +3308,10 @@
         <v>14</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E24" s="6">
         <v>800</v>
@@ -3215,13 +3323,13 @@
         <v>1200</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I24" s="10">
         <v>1</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="78" customHeight="1">
@@ -3232,10 +3340,10 @@
         <v>14</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="E25" s="6">
         <v>1000</v>
@@ -3247,13 +3355,13 @@
         <v>1400</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I25" s="10">
         <v>1</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="78" customHeight="1">
@@ -3264,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="E26" s="6">
         <v>600</v>
@@ -3279,13 +3387,13 @@
         <v>900</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I26" s="10">
         <v>1</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="78" customHeight="1">
@@ -3299,7 +3407,7 @@
         <v>74</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E27" s="6">
         <v>600</v>
@@ -3311,13 +3419,13 @@
         <v>800</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="78" customHeight="1">
@@ -3328,10 +3436,10 @@
         <v>14</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="E28" s="6">
         <v>1000</v>
@@ -3343,13 +3451,13 @@
         <v>1500</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I28" s="10">
         <v>1</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="78" customHeight="1">
@@ -3360,10 +3468,10 @@
         <v>16</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E29" s="6">
         <v>1800</v>
@@ -3375,13 +3483,13 @@
         <v>2200</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I29" s="10">
         <v>1</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="78" customHeight="1">
@@ -3392,10 +3500,10 @@
         <v>16</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E30" s="6">
         <v>2000</v>
@@ -3407,13 +3515,13 @@
         <v>2500</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I30" s="10">
         <v>1</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="78" customHeight="1">
@@ -3424,10 +3532,10 @@
         <v>16</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E31" s="6">
         <v>1900</v>
@@ -3439,13 +3547,13 @@
         <v>2500</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="78" customHeight="1">
@@ -3456,10 +3564,10 @@
         <v>16</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E32" s="6">
         <v>1800</v>
@@ -3471,13 +3579,13 @@
         <v>2200</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I32" s="10">
         <v>1</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="78" customHeight="1">
@@ -3488,10 +3596,10 @@
         <v>16</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E33" s="6">
         <v>1500</v>
@@ -3503,13 +3611,13 @@
         <v>1900</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I33" s="10">
         <v>1</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="78" customHeight="1">
@@ -3520,10 +3628,10 @@
         <v>16</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E34" s="6">
         <v>1000</v>
@@ -3535,13 +3643,13 @@
         <v>1400</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I34" s="10">
         <v>1</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="78" customHeight="1">
@@ -3552,10 +3660,10 @@
         <v>16</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E35" s="6">
         <v>300</v>
@@ -3567,13 +3675,13 @@
         <v>400</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I35" s="10">
         <v>1</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="78" customHeight="1">
@@ -3584,10 +3692,10 @@
         <v>18</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E36" s="6">
         <v>3000</v>
@@ -3599,13 +3707,13 @@
         <v>3500</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="I36" s="10">
         <v>1</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="78" customHeight="1">
@@ -3616,10 +3724,10 @@
         <v>18</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E37" s="6">
         <v>2000</v>
@@ -3631,13 +3739,13 @@
         <v>2600</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="I37" s="10">
         <v>1</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="78" customHeight="1">
@@ -3648,10 +3756,10 @@
         <v>18</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E38" s="6">
         <v>3000</v>
@@ -3663,13 +3771,13 @@
         <v>3500</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="I38" s="10">
         <v>1</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="78" customHeight="1">
@@ -3680,10 +3788,10 @@
         <v>20</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E39" s="6">
         <v>2500</v>
@@ -3695,13 +3803,13 @@
         <v>3000</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="I39" s="10">
         <v>1</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="78" customHeight="1">
@@ -3712,10 +3820,10 @@
         <v>20</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E40" s="6">
         <v>1000</v>
@@ -3727,13 +3835,13 @@
         <v>1400</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="78" customHeight="1">
@@ -3744,10 +3852,10 @@
         <v>22</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E41" s="6">
         <v>1800</v>
@@ -3759,13 +3867,13 @@
         <v>2200</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="I41" s="10">
         <v>0</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="78" customHeight="1">
@@ -3776,10 +3884,10 @@
         <v>22</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="E42" s="6">
         <v>1000</v>
@@ -3791,13 +3899,13 @@
         <v>1400</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="I42" s="10">
         <v>0</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="78" customHeight="1">
@@ -3808,10 +3916,10 @@
         <v>22</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="E43" s="6">
         <v>600</v>
@@ -3823,13 +3931,13 @@
         <v>1000</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="I43" s="10">
         <v>0</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="78" customHeight="1">
@@ -3840,10 +3948,10 @@
         <v>22</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E44" s="6">
         <v>1200</v>
@@ -3855,43 +3963,75 @@
         <v>1800</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="I44" s="10">
         <v>0</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="32" customHeight="1">
-      <c r="C45" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E45" s="8">
-        <f>SUMIF(I6:I44,1,E6:E44)</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="78" customHeight="1">
+      <c r="A45" s="5">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E45" s="6">
+        <v>2500</v>
+      </c>
+      <c r="F45" s="6">
+        <v>5500</v>
+      </c>
+      <c r="G45" s="10">
+        <v>3500</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I45" s="10">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="32" customHeight="1">
+      <c r="C46" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E46" s="8">
+        <f>SUMIF(I6:I45,1,E6:E45)</f>
         <v>98100</v>
       </c>
-      <c r="F45" s="8">
-        <f>SUMIF(I6:I44,1,F6:F44)</f>
+      <c r="F46" s="8">
+        <f>SUMIF(I6:I45,1,F6:F45)</f>
         <v>154100</v>
       </c>
-      <c r="G45" s="8">
-        <f>SUMIF(I6:I44,1,G6:G44)</f>
+      <c r="G46" s="8">
+        <f>SUMIF(I6:I45,1,G6:G45)</f>
         <v>123300</v>
       </c>
-      <c r="J45" s="7" t="s">
-        <v>258</v>
+      <c r="J46" s="7" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J44"/>
+  <autoFilter ref="A5:J45"/>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:J4"/>
   </mergeCells>
-  <dataValidations count="117">
+  <dataValidations count="120">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="当前预留金额" prompt="请输入非负人民币金额，合计会更新。" sqref="G6">
       <formula1>0</formula1>
     </dataValidation>
@@ -4241,6 +4381,15 @@
       <formula1>"0,1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H44">
+      <formula1>"首批,后补,可选"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="当前预留金额" prompt="请输入非负人民币金额，合计会更新。" sqref="G45">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I45">
+      <formula1>"0,1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
       <formula1>"首批,后补,可选"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4269,7 +4418,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4277,7 +4426,7 @@
     </row>
     <row r="2" spans="1:4" ht="34" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4285,41 +4434,41 @@
     </row>
     <row r="5" spans="1:4" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="88" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="88" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>8</v>
@@ -4327,41 +4476,41 @@
     </row>
     <row r="8" spans="1:4" ht="88" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="88" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="88" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>18</v>
@@ -4369,13 +4518,13 @@
     </row>
     <row r="11" spans="1:4" ht="88" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>20</v>
@@ -4383,13 +4532,13 @@
     </row>
     <row r="12" spans="1:4" ht="88" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>22</v>
@@ -4414,7 +4563,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="32" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -4430,7 +4579,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4443,7 +4592,7 @@
     </row>
     <row r="2" spans="1:9" ht="34" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4456,7 +4605,7 @@
     </row>
     <row r="4" spans="1:9" ht="44" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4469,39 +4618,39 @@
     </row>
     <row r="5" spans="1:9" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="68" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C6" s="6">
         <f>预算明细!G6</f>
@@ -4516,10 +4665,10 @@
     </row>
     <row r="7" spans="1:9" ht="68" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C7" s="6">
         <f>预算明细!G7</f>
@@ -4534,10 +4683,10 @@
     </row>
     <row r="8" spans="1:9" ht="68" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C8" s="6">
         <f>预算明细!G8</f>
@@ -4552,10 +4701,10 @@
     </row>
     <row r="9" spans="1:9" ht="68" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C9" s="6">
         <f>预算明细!G9</f>
@@ -4570,10 +4719,10 @@
     </row>
     <row r="10" spans="1:9" ht="68" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C10" s="6">
         <f>预算明细!G10</f>
@@ -4588,10 +4737,10 @@
     </row>
     <row r="11" spans="1:9" ht="68" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C11" s="6">
         <f>预算明细!G11</f>
@@ -4606,10 +4755,10 @@
     </row>
     <row r="12" spans="1:9" ht="68" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C12" s="6">
         <f>预算明细!G12</f>
@@ -4624,10 +4773,10 @@
     </row>
     <row r="13" spans="1:9" ht="68" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C13" s="6">
         <f>预算明细!G13</f>
@@ -4642,10 +4791,10 @@
     </row>
     <row r="14" spans="1:9" ht="68" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C14" s="6">
         <f>预算明细!G14</f>
@@ -4660,10 +4809,10 @@
     </row>
     <row r="15" spans="1:9" ht="68" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C15" s="6">
         <f>预算明细!G15</f>
@@ -4678,10 +4827,10 @@
     </row>
     <row r="16" spans="1:9" ht="68" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C16" s="6">
         <f>预算明细!G16</f>
@@ -4696,10 +4845,10 @@
     </row>
     <row r="17" spans="1:9" ht="68" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C17" s="6">
         <f>预算明细!G17</f>
@@ -4714,10 +4863,10 @@
     </row>
     <row r="18" spans="1:9" ht="68" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C18" s="6">
         <f>预算明细!G18</f>
@@ -4732,10 +4881,10 @@
     </row>
     <row r="19" spans="1:9" ht="68" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C19" s="6">
         <f>预算明细!G19</f>
@@ -4750,10 +4899,10 @@
     </row>
     <row r="20" spans="1:9" ht="68" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C20" s="6">
         <f>预算明细!G20</f>
@@ -4768,10 +4917,10 @@
     </row>
     <row r="21" spans="1:9" ht="68" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C21" s="6">
         <f>预算明细!G21</f>
@@ -4786,10 +4935,10 @@
     </row>
     <row r="22" spans="1:9" ht="60" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C22" s="6">
         <v>0</v>
@@ -4803,10 +4952,10 @@
     </row>
     <row r="23" spans="1:9" ht="46" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C23" s="8">
         <f>SUM(C6:C22)</f>
@@ -4824,6 +4973,24 @@
         <f>IF(COUNT(H6:H22)=0,"",SUM(H6:H22))</f>
         <v/>
       </c>
+    </row>
+    <row r="25" spans="1:9" ht="68" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C25" s="6">
+        <f>预算明细!G45</f>
+        <v>3500</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4845,7 +5012,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="32" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -4856,7 +5023,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4864,7 +5031,7 @@
     </row>
     <row r="2" spans="1:4" ht="34" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4872,226 +5039,254 @@
     </row>
     <row r="5" spans="1:4" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="82" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="82" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="82" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="82" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="82" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="82" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="82" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="82" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="82" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="82" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="82" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>352</v>
+        <v>365</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="82" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>356</v>
+        <v>369</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="82" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="82" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="82" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>368</v>
+        <v>382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="82" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="82" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -5107,6 +5302,8 @@
     <hyperlink ref="D10" r:id="rId5"/>
     <hyperlink ref="D11" r:id="rId6"/>
     <hyperlink ref="D12" r:id="rId7"/>
+    <hyperlink ref="D16" r:id="rId8"/>
+    <hyperlink ref="D17" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>

--- a/预算/装修需求与预算_20261006.xlsx
+++ b/预算/装修需求与预算_20261006.xlsx
@@ -15,14 +15,14 @@
     <sheet name="依据与实测" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">确认需求!$A$5:$D$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">预算明细!$A$5:$J$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">依据与实测!$A$1:$D$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">报价对照!$A$1:$I$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">确认需求!$A$1:$D$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">确认需求!$A$5:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">预算明细!$A$5:$J$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">依据与实测!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">报价对照!$A$1:$I$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">确认需求!$A$1:$D$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">采购节奏!$A$1:$D$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">预算总览!$A$1:$E$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">预算明细!$A$1:$J$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">预算明细!$A$1:$J$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">依据与实测!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">报价对照!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">确认需求!$1:$5</definedName>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="433">
   <si>
     <t>装修需求与预算</t>
   </si>
@@ -139,7 +139,7 @@
     <t>不含下方可选项、电脑硬件、游戏主机和可退装修押金。</t>
   </si>
   <si>
-    <t>未纳入合计的备选：次卧空调、净水器、智能门锁升级、电动窗帘后升级。电脑硬件按用户要求暂不采购；Switch等娱乐硬件另行考虑。</t>
+    <t>未纳入合计的备选：次卧空调、净水器、智能门锁升级、电动窗帘后升级及八处扩充吊柜。电脑硬件按用户要求暂不采购；Switch等娱乐硬件另行考虑。</t>
   </si>
   <si>
     <t>全包询价：请每家公司按同一范围列明拆旧清运、全部门窗、柜体五金、开关灯具、安装收口和管理服务是否包含。已在套餐计入的项目无需再加。</t>
@@ -256,7 +256,10 @@
     <t>收纳</t>
   </si>
   <si>
-    <t>顶柜＋挂衣杆＋帘子，按两人日常衣物量先规划；尚未盘点衣物。</t>
+    <t>主卧182cm组合收纳：125cm干净挂衣、57cm独立脏衣仓、顶柜＋帘杆；未盘点衣物，次卧作补充。</t>
+  </si>
+  <si>
+    <t>原需求保留；尺寸为方案</t>
   </si>
   <si>
     <t>梳妆台</t>
@@ -316,10 +319,10 @@
     <t>餐桌</t>
   </si>
   <si>
-    <t>希望饭桌可收纳；本版采用带抽屉折叠桌，收拢30×80cm、展开120×80cm。</t>
-  </si>
-  <si>
-    <t>收纳要求已确认；尺寸为建议</t>
+    <t>固定餐桌，不再折叠；本版120×70cm，两把餐椅，桌下不加低横撑。</t>
+  </si>
+  <si>
+    <t>固定款已确认；尺寸为方案</t>
   </si>
   <si>
     <t>床朝向</t>
@@ -334,10 +337,10 @@
     <t>新增顶柜</t>
   </si>
   <si>
-    <t>用户希望考虑上方打柜；工位、电视墙、主卧门洞及次卧柜顶先排备选模块。</t>
-  </si>
-  <si>
-    <t>需求已记录；柜量与固定条件待复尺</t>
+    <t>继续找上方柜位；八处扩充吊柜约7.96延米，规划5500元另列可选；基础柜顶和厨房柜不重复。</t>
+  </si>
+  <si>
+    <t>上方收纳需求确认；范围待复尺</t>
   </si>
   <si>
     <t>厨房</t>
@@ -454,6 +457,78 @@
     <t>计划自动换水扫拖机器人，先留基站、上下水、电源与检修空间。</t>
   </si>
   <si>
+    <t>清扫</t>
+  </si>
+  <si>
+    <t>家具底部</t>
+  </si>
+  <si>
+    <t>每处安排机器人可进入清扫或落地封底；柜顶也收口到顶，避免难清理窄缝。</t>
+  </si>
+  <si>
+    <t>用户最新要求</t>
+  </si>
+  <si>
+    <t>验证假设</t>
+  </si>
+  <si>
+    <t>先按38cm直径、14cm高包络，通路45cm、架空家具底16cm；实际设备未选，阈高和受压净空需复尺。</t>
+  </si>
+  <si>
+    <t>助手规划假设，非机器已选</t>
+  </si>
+  <si>
+    <t>入户</t>
+  </si>
+  <si>
+    <t>鞋柜与挂衣</t>
+  </si>
+  <si>
+    <t>入口安排鞋柜、挂外套和换鞋座；本版214×42cm组合柜，避门扇。</t>
+  </si>
+  <si>
+    <t>功能已确认；尺寸为方案</t>
+  </si>
+  <si>
+    <t>可复穿衣物</t>
+  </si>
+  <si>
+    <t>独立壁挂衣板，挂穿过但暂不需要洗的衣物；45cm宽，不与干净衣物或脏衣篮混放。</t>
+  </si>
+  <si>
+    <t>用户要求；位置为方案</t>
+  </si>
+  <si>
+    <t>脏衣篮</t>
+  </si>
+  <si>
+    <t>主卧柜右端独立脏衣仓，带盖篮可抽出，与干净衣物分隔。</t>
+  </si>
+  <si>
+    <t>用户要求；容量待核</t>
+  </si>
+  <si>
+    <t>点位</t>
+  </si>
+  <si>
+    <t>灯具与插排</t>
+  </si>
+  <si>
+    <t>模型补灯具、插座、开关、网口、两工位插排、插头和离地走线；16处灯具、37个电源插座。</t>
+  </si>
+  <si>
+    <t>用户要求；数量为规划</t>
+  </si>
+  <si>
+    <t>例外处理</t>
+  </si>
+  <si>
+    <t>开放淋浴湿区人工清扫；五爪电脑椅移开，设备散热与检修不能因封缝堵住。</t>
+  </si>
+  <si>
+    <t>功能条件说明</t>
+  </si>
+  <si>
     <t>逐项预算与采购范围</t>
   </si>
   <si>
@@ -496,10 +571,10 @@
     <t>水电重做及未来设备预留</t>
   </si>
   <si>
-    <t>按新布局重做；靠阳台两侧单屏工位的插座网口，空调点位，洗烘机、洗碗机、机器人接口，电动窗帘电源。</t>
-  </si>
-  <si>
-    <t>列点位图、回路、水管电线品牌规格及计价方式；窗边桌线缆走墙，避开窗帘和阳台门。此项含管线底盒，面板另核算。</t>
+    <t>灯具线路、37个电源插座、7组开关、4组网口，窗边两工位；空调、窗帘、洗烘机、洗碗机及机器人接口。</t>
+  </si>
+  <si>
+    <t>列完整点位图、回路、管线规格；此行含管线底盒，面板在灯具项。点位为规划，电工现场核定；不要把插排算作固定插座替代。</t>
   </si>
   <si>
     <t>防水、找平及基层修复</t>
@@ -550,7 +625,7 @@
     <t>橱柜、台面、水槽与龙头</t>
   </si>
   <si>
-    <t>约4.7㎡厨房，基础地柜吊柜、台面、水槽龙头；洗碗机以后买，预留柜位。</t>
+    <t>约4.7㎡厨房，基础地柜吊柜、台面、水槽龙头；洗碗机以后买，预留柜位。地柜连续封底，含水槽上方吊柜与常规烟机周边柜。</t>
   </si>
   <si>
     <t>列地柜吊柜长度、转角、台面、五金和安装；柜位必须按拟选洗碗机外尺寸确定。</t>
@@ -568,10 +643,10 @@
     <t>主卧及基础收纳</t>
   </si>
   <si>
-    <t>原需求主卧顶柜＋挂衣杆＋帘子，鞋柜及基础储物；先按两人日常衣物量规划。新增浅顶柜另列备选。</t>
-  </si>
-  <si>
-    <t>列柜体计价方式、板材五金、墙体固定；梳妆台在家具项。主卧原顶柜已计此行，不能在新增顶柜中重复报价。</t>
+    <t>入口214×42cm组合柜（鞋柜120cm、外套60cm、杂物34cm）；主卧182×55cm（125cm干净挂衣＋57cm独立脏衣仓）；次卧110×50cm柜，全部落地封底、顶部收口。</t>
+  </si>
+  <si>
+    <t>包含入口、主卧顶柜和次卧全高柜及帘杆、封板；篮子挂钩配件另列，不重复柜体。新增八处吊柜另列可选；核对承重、板材五金与衣物量。</t>
   </si>
   <si>
     <t>外窗全部换新</t>
@@ -604,10 +679,10 @@
     <t>灯具与普通开关插座面板</t>
   </si>
   <si>
-    <t>基础照明、普通开关插座面板；不做复杂装饰灯。</t>
-  </si>
-  <si>
-    <t>若面板已含在水电套餐，本行扣除对应部分；智能替换部分只在下一行算升级差价。</t>
+    <t>16处灯具（含两台灯及镜灯、床头阅读灯、厨房台面灯），37个电源插座、7组开关、4组网口面板；不做复杂装饰灯。</t>
+  </si>
+  <si>
+    <t>灯具包含适配湿区及安装配件；普通面板如水电套餐已含则扣重，智能件只另计升级差价。灯具数量不等于照度设计已完成。</t>
   </si>
   <si>
     <t>手拉窗帘与轨道</t>
@@ -631,28 +706,28 @@
     <t>主卧床架与床垫</t>
   </si>
   <si>
-    <t>助手建议宽1.8米，床长优先2.1米；窄边床架；两人188cm/100kg与160cm/50kg。</t>
-  </si>
-  <si>
-    <t>本版先按床头左右对调、靠图面右侧墙；完整床架尺寸、试躺与承重需复核；2.1米长款如需定制应明确价格。</t>
+    <t>助手建议宽1.8米，床长优先2.1米；窄边床架；两人188cm/100kg与160cm/50kg。；底部最小净空16cm，最低横梁也须满足。</t>
+  </si>
+  <si>
+    <t>本版先按床头左右对调、靠图面右侧墙；完整床架尺寸、试躺与承重需复核；2.1米长款如需定制应明确价格。床头封墙，受压后净空和支脚位置按实物核对。</t>
   </si>
   <si>
     <t>客厅沙发</t>
   </si>
   <si>
-    <t>保留沙发＋电视/未来游戏主机娱乐区，先按紧凑成品沙发估算。</t>
-  </si>
-  <si>
-    <t>尺寸与电视区、餐区、双人工位及通道一起排布。</t>
+    <t>保留沙发＋电视/未来游戏主机娱乐区，先按紧凑成品沙发估算。底部净空16cm。</t>
+  </si>
+  <si>
+    <t>尺寸与电视区、餐区、双人工位及通道一起排布。按实物最低横撑与受压净空选型。</t>
   </si>
   <si>
     <t>餐桌椅</t>
   </si>
   <si>
-    <t>用户希望可收纳；本版按带抽屉折叠餐桌＋两把可折叠椅，收拢约30×80cm、展开约120×80cm。</t>
-  </si>
-  <si>
-    <t>尺寸为占位建议，实际产品需核对稳定性、桌翼支撑、折叠椅是否能收入；展开前将桌子移出墙边。</t>
+    <t>固定120×70cm餐桌＋两把餐椅；取消折叠方案。桌腿内净99×53cm，椅腿内净约46cm为占位目标。</t>
+  </si>
+  <si>
+    <t>选无低位横撑款，核对实际腿间距、稳定性及承重；餐椅清扫时收近或移开，不靠折叠节省空间。</t>
   </si>
   <si>
     <t>两张电脑桌</t>
@@ -673,10 +748,10 @@
     <t>已有椅子的搬运另与搬家统一考虑。</t>
   </si>
   <si>
-    <t>保留主卧梳妆台需求，暂按紧凑成品款。</t>
-  </si>
-  <si>
-    <t>结合床、挂衣区、窗户和使用通道核对位置。</t>
+    <t>64×40cm悬空梳妆台、镜和紧凑凳；凳体落地封闭可移动。</t>
+  </si>
+  <si>
+    <t>墙体可靠固定条件待核，不可固定时改封底落地柜；梳妆灯在灯具项。</t>
   </si>
   <si>
     <t>入住杂项与开荒保洁</t>
@@ -835,13 +910,40 @@
     <t>未计当前合计；按窗帘数量、轨道长度、型号及安装核对。</t>
   </si>
   <si>
-    <t>新增浅顶柜（方案备选）</t>
-  </si>
-  <si>
-    <t>两个工位上方、电视墙上方、主卧门洞上方及次卧柜补顶层，共约5.48延米；前四处深30cm，次卧延续50cm深。</t>
-  </si>
-  <si>
-    <t>规划估算，未取得柜体报价；需按板材五金、墙体可靠固定、梁和门窗空调净空复尺。主卧原顶柜已计基础收纳，勿重复。</t>
+    <t>新增吊柜（扩充方案备选）</t>
+  </si>
+  <si>
+    <t>两个工位、电视墙、主卧门洞、可复穿衣板、餐区、洗衣区、冰箱上方共八处，约7.96延米；柜深25～40cm。</t>
+  </si>
+  <si>
+    <t>初始不计入总额；底部1.75～2.25m随位置不同、顶2.65m另5cm封板。现场核梁、墙体固定、轨道、设备散热和柜门。基础柜顶与厨房吊柜不重复。</t>
+  </si>
+  <si>
+    <t>工位插排、走线槽与主机托架</t>
+  </si>
+  <si>
+    <t>两个工位各一条插排、固定走线槽、主机离地托架，托架底净空16cm。</t>
+  </si>
+  <si>
+    <t>插排直插墙面不串联，总负荷按实物额定；托架承重按主机，线缆固定离地。电脑硬件仍不计。</t>
+  </si>
+  <si>
+    <t>挂衣钩、可复穿衣板和脏衣篮</t>
+  </si>
+  <si>
+    <t>入口外套挂钩、主卧45cm壁挂衣板及带盖可抽出脏衣篮。</t>
+  </si>
+  <si>
+    <t>柜体已在基础收纳，此行只计配件、壁挂板和篮子；供应商套餐已含时扣除。衣物不垂地，独立脏衣仓通风。</t>
+  </si>
+  <si>
+    <t>洗衣机侧围封板与台面</t>
+  </si>
+  <si>
+    <t>阳台70×109cm洗衣侧围与台面，可拆封板处理外侧窄缝。</t>
+  </si>
+  <si>
+    <t>不堵设备自身通风口；抽机检修、进排水、振动及型号所需散热空隙按说明书复核；洗衣吊柜另列可选。</t>
   </si>
   <si>
     <t>计入项目合计</t>
@@ -868,7 +970,7 @@
     <t>方案及询价</t>
   </si>
   <si>
-    <t>复尺窗边两侧单屏工位、折叠餐桌、沙发电视区、床调向、浅顶柜、门窗与洗衣区。</t>
+    <t>复尺单屏工位、固定餐桌、入口柜、三类衣物、灯电点位与机器人通路、吊柜及门窗洗衣区。</t>
   </si>
   <si>
     <t>设备购买可延后，但冰箱、洗烘机、洗碗机、机器人等拟选型号的外尺寸与安装条件需先确定。</t>
@@ -982,10 +1084,10 @@
     <t>未填写全部必需范围前，合计只是已填金额；未报价/漏项不等于免费。</t>
   </si>
   <si>
-    <t>备选：新增浅顶柜</t>
-  </si>
-  <si>
-    <t>单独报新增五处柜体价格，原主卧顶柜扣重；本行不计入上方同口径必需报价合计。</t>
+    <t>备选：新增八处吊柜</t>
+  </si>
+  <si>
+    <t>单独报新增八处柜体价格，入口、主卧、次卧及厨房基础柜顶扣重；本行不计入上方同口径必需报价合计。</t>
   </si>
   <si>
     <t>资料依据与现场待核</t>
@@ -1117,10 +1219,10 @@
     <t>客餐厅工位布局</t>
   </si>
   <si>
-    <t>两台台式机各一屏；桌子靠阳台两侧墙，中间约82cm通路以58cm椅子收近为前提。餐桌折叠并移出展开。</t>
-  </si>
-  <si>
-    <t>2026-10-06第2版；待复尺</t>
+    <t>两台台式机各一屏；桌子靠阳台两侧墙，中间约82cm通路以58cm椅子收近为前提。固定120×70cm餐桌，机器人通路按45cm包络验算。</t>
+  </si>
+  <si>
+    <t>2026-10-06第4版；待复尺</t>
   </si>
   <si>
     <t>屏幕侧对窗，窗帘控制反光；测实际椅子、窗帘、门洞、线缆和主机。</t>
@@ -1141,7 +1243,7 @@
     <t>新增顶柜固定</t>
   </si>
   <si>
-    <t>柜底先按2.2m、顶2.65m；主卧门洞、工位和电视墙用30cm深浅柜，次卧柜补顶层；不只依靠装饰吊顶承重。</t>
+    <t>八处扩充吊柜底1.75～2.25m，柜顶2.65m另5cm收口；基础柜落地封底，不能只依靠装饰吊顶承重。</t>
   </si>
   <si>
     <t>板材与墙体待现场核对</t>
@@ -1165,13 +1267,37 @@
     <t>洗衣区与机器人</t>
   </si>
   <si>
-    <t>洗烘一体机及机器人基站位置尚未最终定；需检查现有排水、进水、电源、柜深、开门与维修空间。</t>
+    <t>本版洗烘机在阳台右端、基站在卫生间外墙；实际型号未定，需复核排水进水、电源、开门与维修空间。</t>
   </si>
   <si>
     <t>待现场定位</t>
   </si>
   <si>
     <t>所有接口应先确定方案，设备允许后买。</t>
+  </si>
+  <si>
+    <t>机器人尺寸参照</t>
+  </si>
+  <si>
+    <t>X20 Max官方机身Φ350×97mm仅作为尺寸参照；未定自动上下水型号。本版按38cm直径、14cm高包络、45cm通路预留。</t>
+  </si>
+  <si>
+    <t>官方尺寸＋助手留量假设</t>
+  </si>
+  <si>
+    <t>https://www.mi.com/sg/product/xiaomi-robot-vacuum-x20-max/specs/</t>
+  </si>
+  <si>
+    <t>插排使用参照</t>
+  </si>
+  <si>
+    <t>工位各一条固定插排、直插墙面，总功率按实物额定；不放在厨卫湿处，线缆离地收束。</t>
+  </si>
+  <si>
+    <t>型号采购时核对</t>
+  </si>
+  <si>
+    <t>https://www.mi.com/chaxianban2/specs</t>
   </si>
   <si>
     <t>拆墙与旧基层</t>
@@ -1788,16 +1914,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A7,预算明细!I6:I45,1)</f>
-        <v>53100</v>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!B6:B48,A7,预算明细!I6:I48,1)</f>
+        <v>56100</v>
       </c>
       <c r="C7" s="6">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A7,预算明细!I6:I45,1)</f>
-        <v>79000</v>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!B6:B48,A7,预算明细!I6:I48,1)</f>
+        <v>85200</v>
       </c>
       <c r="D7" s="6">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A7,预算明细!I6:I45,1)</f>
-        <v>65200</v>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!B6:B48,A7,预算明细!I6:I48,1)</f>
+        <v>69000</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>9</v>
@@ -1808,15 +1934,15 @@
         <v>10</v>
       </c>
       <c r="B8" s="6">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A8,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!B6:B48,A8,预算明细!I6:I48,1)</f>
         <v>10100</v>
       </c>
       <c r="C8" s="6">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A8,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!B6:B48,A8,预算明细!I6:I48,1)</f>
         <v>17500</v>
       </c>
       <c r="D8" s="6">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A8,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!B6:B48,A8,预算明细!I6:I48,1)</f>
         <v>13000</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -1828,16 +1954,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="6">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A9,预算明细!I6:I45,1)</f>
-        <v>3800</v>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!B6:B48,A9,预算明细!I6:I48,1)</f>
+        <v>4400</v>
       </c>
       <c r="C9" s="6">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A9,预算明细!I6:I45,1)</f>
-        <v>7000</v>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!B6:B48,A9,预算明细!I6:I48,1)</f>
+        <v>8300</v>
       </c>
       <c r="D9" s="6">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A9,预算明细!I6:I45,1)</f>
-        <v>5200</v>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!B6:B48,A9,预算明细!I6:I48,1)</f>
+        <v>6000</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>13</v>
@@ -1848,16 +1974,16 @@
         <v>14</v>
       </c>
       <c r="B10" s="6">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A10,预算明细!I6:I45,1)</f>
-        <v>9300</v>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!B6:B48,A10,预算明细!I6:I48,1)</f>
+        <v>10100</v>
       </c>
       <c r="C10" s="6">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A10,预算明细!I6:I45,1)</f>
-        <v>16500</v>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!B6:B48,A10,预算明细!I6:I48,1)</f>
+        <v>18500</v>
       </c>
       <c r="D10" s="6">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A10,预算明细!I6:I45,1)</f>
-        <v>12800</v>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!B6:B48,A10,预算明细!I6:I48,1)</f>
+        <v>14000</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>15</v>
@@ -1868,15 +1994,15 @@
         <v>16</v>
       </c>
       <c r="B11" s="6">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A11,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!B6:B48,A11,预算明细!I6:I48,1)</f>
         <v>10300</v>
       </c>
       <c r="C11" s="6">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A11,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!B6:B48,A11,预算明细!I6:I48,1)</f>
         <v>15800</v>
       </c>
       <c r="D11" s="6">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A11,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!B6:B48,A11,预算明细!I6:I48,1)</f>
         <v>13100</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -1888,15 +2014,15 @@
         <v>18</v>
       </c>
       <c r="B12" s="6">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A12,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!B6:B48,A12,预算明细!I6:I48,1)</f>
         <v>8000</v>
       </c>
       <c r="C12" s="6">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A12,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!B6:B48,A12,预算明细!I6:I48,1)</f>
         <v>12500</v>
       </c>
       <c r="D12" s="6">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A12,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!B6:B48,A12,预算明细!I6:I48,1)</f>
         <v>9600</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -1908,15 +2034,15 @@
         <v>20</v>
       </c>
       <c r="B13" s="6">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A13,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!B6:B48,A13,预算明细!I6:I48,1)</f>
         <v>3500</v>
       </c>
       <c r="C13" s="6">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A13,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!B6:B48,A13,预算明细!I6:I48,1)</f>
         <v>5800</v>
       </c>
       <c r="D13" s="6">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A13,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!B6:B48,A13,预算明细!I6:I48,1)</f>
         <v>4400</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -1928,15 +2054,15 @@
         <v>22</v>
       </c>
       <c r="B14" s="6">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!B6:B45,A14,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!B6:B48,A14,预算明细!I6:I48,1)</f>
         <v>0</v>
       </c>
       <c r="C14" s="6">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!B6:B45,A14,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!B6:B48,A14,预算明细!I6:I48,1)</f>
         <v>0</v>
       </c>
       <c r="D14" s="6">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!B6:B45,A14,预算明细!I6:I45,1)</f>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!B6:B48,A14,预算明细!I6:I48,1)</f>
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -1948,16 +2074,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="8">
-        <f>SUMIFS(预算明细!E6:E45,预算明细!H6:H45,"首批",预算明细!I6:I45,1)</f>
-        <v>86600</v>
+        <f>SUMIFS(预算明细!E6:E48,预算明细!H6:H48,"首批",预算明细!I6:I48,1)</f>
+        <v>91000</v>
       </c>
       <c r="C16" s="8">
-        <f>SUMIFS(预算明细!F6:F45,预算明细!H6:H45,"首批",预算明细!I6:I45,1)</f>
-        <v>135800</v>
+        <f>SUMIFS(预算明细!F6:F48,预算明细!H6:H48,"首批",预算明细!I6:I48,1)</f>
+        <v>145300</v>
       </c>
       <c r="D16" s="8">
-        <f>SUMIFS(预算明细!G6:G45,预算明细!H6:H45,"首批",预算明细!I6:I45,1)</f>
-        <v>109300</v>
+        <f>SUMIFS(预算明细!G6:G48,预算明细!H6:H48,"首批",预算明细!I6:I48,1)</f>
+        <v>115100</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>25</v>
@@ -1969,15 +2095,15 @@
       </c>
       <c r="B17" s="8">
         <f>CEILING(B16*10%,100)</f>
-        <v>8700</v>
+        <v>9100</v>
       </c>
       <c r="C17" s="8">
         <f>CEILING(C16*10%,100)</f>
-        <v>13600</v>
+        <v>14600</v>
       </c>
       <c r="D17" s="8">
         <f>CEILING(D16*10%,100)</f>
-        <v>11000</v>
+        <v>11600</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>27</v>
@@ -1989,15 +2115,15 @@
       </c>
       <c r="B18" s="8">
         <f>B16+B17</f>
-        <v>95300</v>
+        <v>100100</v>
       </c>
       <c r="C18" s="8">
         <f>C16+C17</f>
-        <v>149400</v>
+        <v>159900</v>
       </c>
       <c r="D18" s="8">
         <f>D16+D17</f>
-        <v>120300</v>
+        <v>126700</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>29</v>
@@ -2008,15 +2134,15 @@
         <v>30</v>
       </c>
       <c r="B20" s="8">
-        <f>SUMIF(预算明细!I6:I45,1,预算明细!E6:E45)-B16</f>
+        <f>SUMIF(预算明细!I6:I48,1,预算明细!E6:E48)-B16</f>
         <v>11500</v>
       </c>
       <c r="C20" s="8">
-        <f>SUMIF(预算明细!I6:I45,1,预算明细!F6:F45)-C16</f>
+        <f>SUMIF(预算明细!I6:I48,1,预算明细!F6:F48)-C16</f>
         <v>18300</v>
       </c>
       <c r="D20" s="8">
-        <f>SUMIF(预算明细!I6:I45,1,预算明细!G6:G45)-D16</f>
+        <f>SUMIF(预算明细!I6:I48,1,预算明细!G6:G48)-D16</f>
         <v>14000</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -2029,15 +2155,15 @@
       </c>
       <c r="B21" s="8">
         <f>B18+B20</f>
-        <v>106800</v>
+        <v>111600</v>
       </c>
       <c r="C21" s="8">
         <f>C18+C20</f>
-        <v>167700</v>
+        <v>178200</v>
       </c>
       <c r="D21" s="8">
         <f>D18+D20</f>
-        <v>134300</v>
+        <v>140700</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>33</v>
@@ -2093,7 +2219,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="32" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -2305,7 +2431,7 @@
         <v>73</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="44" customHeight="1">
@@ -2313,24 +2439,24 @@
         <v>68</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="44" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>47</v>
@@ -2338,13 +2464,13 @@
     </row>
     <row r="20" spans="1:4" ht="44" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>47</v>
@@ -2352,41 +2478,41 @@
     </row>
     <row r="21" spans="1:4" ht="44" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="44" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="44" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>47</v>
@@ -2394,16 +2520,16 @@
     </row>
     <row r="24" spans="1:4" ht="44" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="44" customHeight="1">
@@ -2411,13 +2537,13 @@
         <v>68</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="44" customHeight="1">
@@ -2425,24 +2551,24 @@
         <v>72</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="44" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>47</v>
@@ -2450,13 +2576,13 @@
     </row>
     <row r="28" spans="1:4" ht="44" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>47</v>
@@ -2464,13 +2590,13 @@
     </row>
     <row r="29" spans="1:4" ht="44" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>47</v>
@@ -2478,27 +2604,27 @@
     </row>
     <row r="30" spans="1:4" ht="44" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="44" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>47</v>
@@ -2506,41 +2632,41 @@
     </row>
     <row r="32" spans="1:4" ht="44" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="44" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="44" customHeight="1">
       <c r="A34" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>47</v>
@@ -2548,13 +2674,13 @@
     </row>
     <row r="35" spans="1:4" ht="44" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>47</v>
@@ -2562,13 +2688,13 @@
     </row>
     <row r="36" spans="1:4" ht="44" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>47</v>
@@ -2576,13 +2702,13 @@
     </row>
     <row r="37" spans="1:4" ht="44" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>47</v>
@@ -2590,34 +2716,132 @@
     </row>
     <row r="38" spans="1:4" ht="44" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="44" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="44" customHeight="1">
+      <c r="A40" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="44" customHeight="1">
+      <c r="A41" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="44" customHeight="1">
+      <c r="A42" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="44" customHeight="1">
+      <c r="A43" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="44" customHeight="1">
+      <c r="A44" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="44" customHeight="1">
+      <c r="A45" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="44" customHeight="1">
+      <c r="A46" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:D39"/>
+  <autoFilter ref="A5:D46"/>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -2637,7 +2861,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="32" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -2652,7 +2876,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2666,7 +2890,7 @@
     </row>
     <row r="2" spans="1:10" ht="34" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2680,7 +2904,7 @@
     </row>
     <row r="4" spans="1:10" ht="40" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2694,16 +2918,16 @@
     </row>
     <row r="5" spans="1:10" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>4</v>
@@ -2715,13 +2939,13 @@
         <v>6</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="78" customHeight="1">
@@ -2732,10 +2956,10 @@
         <v>8</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="E6" s="6">
         <v>6000</v>
@@ -2747,13 +2971,13 @@
         <v>7500</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I6" s="10">
         <v>1</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="78" customHeight="1">
@@ -2764,28 +2988,28 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="E7" s="6">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="F7" s="6">
-        <v>11000</v>
+        <v>13000</v>
       </c>
       <c r="G7" s="10">
-        <v>9500</v>
+        <v>10500</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I7" s="10">
         <v>1</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="78" customHeight="1">
@@ -2796,10 +3020,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="E8" s="6">
         <v>4500</v>
@@ -2811,13 +3035,13 @@
         <v>6000</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="78" customHeight="1">
@@ -2828,10 +3052,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="E9" s="6">
         <v>11000</v>
@@ -2843,13 +3067,13 @@
         <v>13000</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I9" s="10">
         <v>1</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="78" customHeight="1">
@@ -2860,10 +3084,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="E10" s="6">
         <v>5500</v>
@@ -2875,13 +3099,13 @@
         <v>6500</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I10" s="10">
         <v>1</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="78" customHeight="1">
@@ -2892,10 +3116,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E11" s="6">
         <v>1800</v>
@@ -2907,13 +3131,13 @@
         <v>2200</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I11" s="10">
         <v>1</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="78" customHeight="1">
@@ -2924,10 +3148,10 @@
         <v>8</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="E12" s="6">
         <v>3500</v>
@@ -2939,13 +3163,13 @@
         <v>4500</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I12" s="10">
         <v>1</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="78" customHeight="1">
@@ -2956,10 +3180,10 @@
         <v>8</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="E13" s="6">
         <v>6500</v>
@@ -2971,13 +3195,13 @@
         <v>8000</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I13" s="10">
         <v>1</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="78" customHeight="1">
@@ -2988,10 +3212,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="E14" s="6">
         <v>2800</v>
@@ -3003,13 +3227,13 @@
         <v>3500</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I14" s="10">
         <v>1</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="78" customHeight="1">
@@ -3020,28 +3244,28 @@
         <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="E15" s="6">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="F15" s="6">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="G15" s="10">
-        <v>4500</v>
+        <v>6500</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="78" customHeight="1">
@@ -3052,10 +3276,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="E16" s="6">
         <v>7000</v>
@@ -3067,13 +3291,13 @@
         <v>9000</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I16" s="10">
         <v>1</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="78" customHeight="1">
@@ -3084,10 +3308,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="E17" s="6">
         <v>2500</v>
@@ -3099,13 +3323,13 @@
         <v>3000</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I17" s="10">
         <v>1</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="78" customHeight="1">
@@ -3116,10 +3340,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="E18" s="6">
         <v>600</v>
@@ -3131,13 +3355,13 @@
         <v>1000</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I18" s="10">
         <v>1</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="78" customHeight="1">
@@ -3148,28 +3372,28 @@
         <v>12</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="E19" s="6">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="F19" s="6">
-        <v>3000</v>
+        <v>4300</v>
       </c>
       <c r="G19" s="10">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I19" s="10">
         <v>1</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="78" customHeight="1">
@@ -3180,10 +3404,10 @@
         <v>12</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="E20" s="6">
         <v>1200</v>
@@ -3195,13 +3419,13 @@
         <v>1600</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I20" s="10">
         <v>1</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="78" customHeight="1">
@@ -3212,10 +3436,10 @@
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="E21" s="6">
         <v>800</v>
@@ -3227,13 +3451,13 @@
         <v>1200</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I21" s="10">
         <v>1</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="78" customHeight="1">
@@ -3244,10 +3468,10 @@
         <v>14</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="E22" s="6">
         <v>3500</v>
@@ -3259,13 +3483,13 @@
         <v>4500</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I22" s="10">
         <v>1</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="78" customHeight="1">
@@ -3276,10 +3500,10 @@
         <v>14</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="E23" s="6">
         <v>1800</v>
@@ -3291,13 +3515,13 @@
         <v>2500</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I23" s="10">
         <v>1</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="78" customHeight="1">
@@ -3308,28 +3532,28 @@
         <v>14</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="E24" s="6">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F24" s="6">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="G24" s="10">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I24" s="10">
         <v>1</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="78" customHeight="1">
@@ -3340,10 +3564,10 @@
         <v>14</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="E25" s="6">
         <v>1000</v>
@@ -3355,13 +3579,13 @@
         <v>1400</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I25" s="10">
         <v>1</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="78" customHeight="1">
@@ -3372,10 +3596,10 @@
         <v>14</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="E26" s="6">
         <v>600</v>
@@ -3387,13 +3611,13 @@
         <v>900</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I26" s="10">
         <v>1</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="78" customHeight="1">
@@ -3404,10 +3628,10 @@
         <v>14</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="E27" s="6">
         <v>600</v>
@@ -3419,13 +3643,13 @@
         <v>800</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="78" customHeight="1">
@@ -3436,10 +3660,10 @@
         <v>14</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="E28" s="6">
         <v>1000</v>
@@ -3451,13 +3675,13 @@
         <v>1500</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I28" s="10">
         <v>1</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="78" customHeight="1">
@@ -3468,10 +3692,10 @@
         <v>16</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="E29" s="6">
         <v>1800</v>
@@ -3483,13 +3707,13 @@
         <v>2200</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I29" s="10">
         <v>1</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="78" customHeight="1">
@@ -3500,10 +3724,10 @@
         <v>16</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="E30" s="6">
         <v>2000</v>
@@ -3515,13 +3739,13 @@
         <v>2500</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I30" s="10">
         <v>1</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="78" customHeight="1">
@@ -3532,10 +3756,10 @@
         <v>16</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="E31" s="6">
         <v>1900</v>
@@ -3547,13 +3771,13 @@
         <v>2500</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="78" customHeight="1">
@@ -3564,10 +3788,10 @@
         <v>16</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="E32" s="6">
         <v>1800</v>
@@ -3579,13 +3803,13 @@
         <v>2200</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I32" s="10">
         <v>1</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="78" customHeight="1">
@@ -3596,10 +3820,10 @@
         <v>16</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="E33" s="6">
         <v>1500</v>
@@ -3611,13 +3835,13 @@
         <v>1900</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I33" s="10">
         <v>1</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="78" customHeight="1">
@@ -3628,10 +3852,10 @@
         <v>16</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="E34" s="6">
         <v>1000</v>
@@ -3643,13 +3867,13 @@
         <v>1400</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I34" s="10">
         <v>1</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="78" customHeight="1">
@@ -3660,10 +3884,10 @@
         <v>16</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="E35" s="6">
         <v>300</v>
@@ -3675,13 +3899,13 @@
         <v>400</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I35" s="10">
         <v>1</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="78" customHeight="1">
@@ -3692,10 +3916,10 @@
         <v>18</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="E36" s="6">
         <v>3000</v>
@@ -3707,13 +3931,13 @@
         <v>3500</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="I36" s="10">
         <v>1</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="78" customHeight="1">
@@ -3724,10 +3948,10 @@
         <v>18</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="E37" s="6">
         <v>2000</v>
@@ -3739,13 +3963,13 @@
         <v>2600</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="I37" s="10">
         <v>1</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="78" customHeight="1">
@@ -3756,10 +3980,10 @@
         <v>18</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="E38" s="6">
         <v>3000</v>
@@ -3771,13 +3995,13 @@
         <v>3500</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="I38" s="10">
         <v>1</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="78" customHeight="1">
@@ -3788,10 +4012,10 @@
         <v>20</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="E39" s="6">
         <v>2500</v>
@@ -3803,13 +4027,13 @@
         <v>3000</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="I39" s="10">
         <v>1</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="78" customHeight="1">
@@ -3820,10 +4044,10 @@
         <v>20</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E40" s="6">
         <v>1000</v>
@@ -3835,13 +4059,13 @@
         <v>1400</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="78" customHeight="1">
@@ -3852,10 +4076,10 @@
         <v>22</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="E41" s="6">
         <v>1800</v>
@@ -3867,13 +4091,13 @@
         <v>2200</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="I41" s="10">
         <v>0</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="78" customHeight="1">
@@ -3884,10 +4108,10 @@
         <v>22</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="E42" s="6">
         <v>1000</v>
@@ -3899,13 +4123,13 @@
         <v>1400</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="I42" s="10">
         <v>0</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="78" customHeight="1">
@@ -3916,10 +4140,10 @@
         <v>22</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="E43" s="6">
         <v>600</v>
@@ -3931,13 +4155,13 @@
         <v>1000</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="I43" s="10">
         <v>0</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="78" customHeight="1">
@@ -3948,10 +4172,10 @@
         <v>22</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="E44" s="6">
         <v>1200</v>
@@ -3963,13 +4187,13 @@
         <v>1800</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="I44" s="10">
         <v>0</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="78" customHeight="1">
@@ -3980,58 +4204,154 @@
         <v>22</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="E45" s="6">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="F45" s="6">
+        <v>8000</v>
+      </c>
+      <c r="G45" s="10">
         <v>5500</v>
       </c>
-      <c r="G45" s="10">
-        <v>3500</v>
-      </c>
       <c r="H45" s="10" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="I45" s="10">
         <v>0</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="32" customHeight="1">
-      <c r="C46" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="E46" s="8">
-        <f>SUMIF(I6:I45,1,E6:E45)</f>
-        <v>98100</v>
-      </c>
-      <c r="F46" s="8">
-        <f>SUMIF(I6:I45,1,F6:F45)</f>
-        <v>154100</v>
-      </c>
-      <c r="G46" s="8">
-        <f>SUMIF(I6:I45,1,G6:G45)</f>
-        <v>123300</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>270</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="78" customHeight="1">
+      <c r="A46" s="9">
+        <v>41</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E46" s="6">
+        <v>300</v>
+      </c>
+      <c r="F46" s="6">
+        <v>800</v>
+      </c>
+      <c r="G46" s="10">
+        <v>500</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="I46" s="10">
+        <v>1</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="78" customHeight="1">
+      <c r="A47" s="5">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E47" s="6">
+        <v>300</v>
+      </c>
+      <c r="F47" s="6">
+        <v>800</v>
+      </c>
+      <c r="G47" s="10">
+        <v>500</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="I47" s="10">
+        <v>1</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="78" customHeight="1">
+      <c r="A48" s="9">
+        <v>43</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E48" s="6">
+        <v>500</v>
+      </c>
+      <c r="F48" s="6">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="10">
+        <v>800</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="I48" s="10">
+        <v>1</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" ht="32" customHeight="1">
+      <c r="C49" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E49" s="8">
+        <f>SUMIF(I6:I48,1,E6:E48)</f>
+        <v>102500</v>
+      </c>
+      <c r="F49" s="8">
+        <f>SUMIF(I6:I48,1,F6:F48)</f>
+        <v>163600</v>
+      </c>
+      <c r="G49" s="8">
+        <f>SUMIF(I6:I48,1,G6:G48)</f>
+        <v>129100</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J45"/>
+  <autoFilter ref="A5:J48"/>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:J4"/>
   </mergeCells>
-  <dataValidations count="120">
+  <dataValidations count="129">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="当前预留金额" prompt="请输入非负人民币金额，合计会更新。" sqref="G6">
       <formula1>0</formula1>
     </dataValidation>
@@ -4390,6 +4710,33 @@
       <formula1>"0,1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H45">
+      <formula1>"首批,后补,可选"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="当前预留金额" prompt="请输入非负人民币金额，合计会更新。" sqref="G46">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I46">
+      <formula1>"0,1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46">
+      <formula1>"首批,后补,可选"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="当前预留金额" prompt="请输入非负人民币金额，合计会更新。" sqref="G47">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I47">
+      <formula1>"0,1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47">
+      <formula1>"首批,后补,可选"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="当前预留金额" prompt="请输入非负人民币金额，合计会更新。" sqref="G48">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48">
+      <formula1>"0,1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48">
       <formula1>"首批,后补,可选"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4418,7 +4765,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4426,7 +4773,7 @@
     </row>
     <row r="2" spans="1:4" ht="34" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4434,41 +4781,41 @@
     </row>
     <row r="5" spans="1:4" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="88" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="88" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>8</v>
@@ -4476,41 +4823,41 @@
     </row>
     <row r="8" spans="1:4" ht="88" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="88" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>290</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="88" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>18</v>
@@ -4518,13 +4865,13 @@
     </row>
     <row r="11" spans="1:4" ht="88" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>20</v>
@@ -4532,13 +4879,13 @@
     </row>
     <row r="12" spans="1:4" ht="88" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>22</v>
@@ -4563,7 +4910,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="32" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -4579,7 +4926,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4592,7 +4939,7 @@
     </row>
     <row r="2" spans="1:9" ht="34" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4605,7 +4952,7 @@
     </row>
     <row r="4" spans="1:9" ht="44" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4618,39 +4965,39 @@
     </row>
     <row r="5" spans="1:9" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>304</v>
+        <v>338</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="68" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C6" s="6">
         <f>预算明细!G6</f>
@@ -4665,14 +5012,14 @@
     </row>
     <row r="7" spans="1:9" ht="68" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C7" s="6">
         <f>预算明细!G7</f>
-        <v>9500</v>
+        <v>10500</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -4683,10 +5030,10 @@
     </row>
     <row r="8" spans="1:9" ht="68" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C8" s="6">
         <f>预算明细!G8</f>
@@ -4701,10 +5048,10 @@
     </row>
     <row r="9" spans="1:9" ht="68" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C9" s="6">
         <f>预算明细!G9</f>
@@ -4719,10 +5066,10 @@
     </row>
     <row r="10" spans="1:9" ht="68" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="C10" s="6">
         <f>预算明细!G10</f>
@@ -4737,10 +5084,10 @@
     </row>
     <row r="11" spans="1:9" ht="68" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C11" s="6">
         <f>预算明细!G11</f>
@@ -4755,10 +5102,10 @@
     </row>
     <row r="12" spans="1:9" ht="68" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C12" s="6">
         <f>预算明细!G12</f>
@@ -4773,10 +5120,10 @@
     </row>
     <row r="13" spans="1:9" ht="68" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C13" s="6">
         <f>预算明细!G13</f>
@@ -4791,10 +5138,10 @@
     </row>
     <row r="14" spans="1:9" ht="68" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C14" s="6">
         <f>预算明细!G14</f>
@@ -4809,14 +5156,14 @@
     </row>
     <row r="15" spans="1:9" ht="68" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C15" s="6">
         <f>预算明细!G15</f>
-        <v>4500</v>
+        <v>6500</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
@@ -4827,10 +5174,10 @@
     </row>
     <row r="16" spans="1:9" ht="68" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C16" s="6">
         <f>预算明细!G16</f>
@@ -4845,10 +5192,10 @@
     </row>
     <row r="17" spans="1:9" ht="68" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="C17" s="6">
         <f>预算明细!G17</f>
@@ -4863,10 +5210,10 @@
     </row>
     <row r="18" spans="1:9" ht="68" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="C18" s="6">
         <f>预算明细!G18</f>
@@ -4881,14 +5228,14 @@
     </row>
     <row r="19" spans="1:9" ht="68" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C19" s="6">
         <f>预算明细!G19</f>
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
@@ -4899,10 +5246,10 @@
     </row>
     <row r="20" spans="1:9" ht="68" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C20" s="6">
         <f>预算明细!G20</f>
@@ -4917,10 +5264,10 @@
     </row>
     <row r="21" spans="1:9" ht="68" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="C21" s="6">
         <f>预算明细!G21</f>
@@ -4933,15 +5280,16 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" ht="60" customHeight="1">
+    <row r="22" spans="1:9" ht="68" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="C22" s="6">
-        <v>0</v>
+        <f>预算明细!G48</f>
+        <v>800</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -4950,47 +5298,64 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" ht="46" customHeight="1">
-      <c r="A23" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="C23" s="8">
-        <f>SUM(C6:C22)</f>
-        <v>83400</v>
-      </c>
-      <c r="D23" s="8">
-        <f>IF(COUNT(D6:D22)=0,"",SUM(D6:D22))</f>
+    <row r="23" spans="1:9" ht="60" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" ht="46" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C24" s="8">
+        <f>SUM(C6:C23)</f>
+        <v>88000</v>
+      </c>
+      <c r="D24" s="8">
+        <f>IF(COUNT(D6:D23)=0,"",SUM(D6:D23))</f>
         <v/>
       </c>
-      <c r="F23" s="8">
-        <f>IF(COUNT(F6:F22)=0,"",SUM(F6:F22))</f>
+      <c r="F24" s="8">
+        <f>IF(COUNT(F6:F23)=0,"",SUM(F6:F23))</f>
         <v/>
       </c>
-      <c r="H23" s="8">
-        <f>IF(COUNT(H6:H22)=0,"",SUM(H6:H22))</f>
+      <c r="H24" s="8">
+        <f>IF(COUNT(H6:H23)=0,"",SUM(H6:H23))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="68" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="C25" s="6">
+    <row r="26" spans="1:9" ht="68" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="6">
         <f>预算明细!G45</f>
-        <v>3500</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
+        <v>5500</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5012,7 +5377,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="32" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -5023,7 +5388,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5031,7 +5396,7 @@
     </row>
     <row r="2" spans="1:4" ht="34" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5039,254 +5404,282 @@
     </row>
     <row r="5" spans="1:4" ht="32" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="82" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>324</v>
+        <v>358</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="82" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="82" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="82" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="82" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="82" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="82" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="82" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="82" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="82" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="82" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="82" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="82" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="82" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="82" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>382</v>
+        <v>415</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="82" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>386</v>
+        <v>419</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="82" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>390</v>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="82" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="82" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -5304,6 +5697,8 @@
     <hyperlink ref="D12" r:id="rId7"/>
     <hyperlink ref="D16" r:id="rId8"/>
     <hyperlink ref="D17" r:id="rId9"/>
+    <hyperlink ref="D20" r:id="rId10"/>
+    <hyperlink ref="D21" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>

--- a/预算/装修需求与预算_20261006.xlsx
+++ b/预算/装修需求与预算_20261006.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预算总览" sheetId="1" r:id="Reb4786701f4f43e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="确认需求" sheetId="2" r:id="Rd46a34555338430e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预算明细" sheetId="3" r:id="R31cc379b2fbc4583"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购节奏" sheetId="4" r:id="Rd0af438d57e14208"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="报价对照" sheetId="5" r:id="R04435e2f6dd94d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="依据与实测" sheetId="6" r:id="R3232f7d0b3414db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬装前置" sheetId="7" r:id="Rd280662423d04be3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预算总览" sheetId="1" r:id="Rcffb392254364f5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="确认需求" sheetId="2" r:id="R9a80d61177aa4da5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预算明细" sheetId="3" r:id="R24ee595dcc144708"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购节奏" sheetId="4" r:id="Rc8fe8c35f10a4c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="报价对照" sheetId="5" r:id="R8ca48eb685444e76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="依据与实测" sheetId="6" r:id="R9e7159cd9df148b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬装前置" sheetId="7" r:id="R79f3e62e9f064151"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -97,7 +97,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -179,6 +179,9 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -187,7 +190,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BudgetItems" displayName="BudgetItems" ref="A5:M51" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BudgetItems" displayName="BudgetItems" ref="A5:M53" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="分类"/>
     <x:tableColumn id="2" name="项目"/>
@@ -486,24 +489,23 @@
         <x:v>1 硬装施工</x:v>
       </x:c>
       <x:c r="B7" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$H$6:$H$51,'预算明细'!$F$6:$F$51,$A7)</x:f>
-        <x:v>72100</x:v>
+        <x:f>SUMIFS('预算明细'!$H$6:$H$53,'预算明细'!$F$6:$F$53,$A7)</x:f>
+        <x:v>73350</x:v>
       </x:c>
       <x:c r="C7" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$I$6:$I$51,'预算明细'!$F$6:$F$51,$A7)</x:f>
-        <x:v>112300</x:v>
+        <x:f>SUMIFS('预算明细'!$I$6:$I$53,'预算明细'!$F$6:$F$53,$A7)</x:f>
+        <x:v>115400</x:v>
       </x:c>
       <x:c r="D7" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$J$6:$J$51,'预算明细'!$F$6:$F$51,$A7)</x:f>
-        <x:v>89660</x:v>
+        <x:f>SUMIFS('预算明细'!$J$6:$J$53,'预算明细'!$F$6:$F$53,$A7)</x:f>
+        <x:v>91460</x:v>
       </x:c>
       <x:c r="E7" s="8" t="n">
         <x:f>D7+D13</x:f>
-        <x:v>101260</x:v>
+        <x:v>103260</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
-        <x:v>施工、门窗、固定柜、固定灯、烟灶热水器。应急金统一留
-此阶段。</x:v>
+        <x:v>施工、门窗、固定柜灯、烟灶热水器；含门外洗漱接口与两设备柜。应急金统一留此阶段。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="65" customHeight="1">
@@ -511,15 +513,15 @@
         <x:v>2 入住必需</x:v>
       </x:c>
       <x:c r="B8" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$H$6:$H$51,'预算明细'!$F$6:$F$51,$A8)</x:f>
+        <x:f>SUMIFS('预算明细'!$H$6:$H$53,'预算明细'!$F$6:$F$53,$A8)</x:f>
         <x:v>19600</x:v>
       </x:c>
       <x:c r="C8" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$I$6:$I$51,'预算明细'!$F$6:$F$51,$A8)</x:f>
+        <x:f>SUMIFS('预算明细'!$I$6:$I$53,'预算明细'!$F$6:$F$53,$A8)</x:f>
         <x:v>34400</x:v>
       </x:c>
       <x:c r="D8" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$J$6:$J$51,'预算明细'!$F$6:$F$51,$A8)</x:f>
+        <x:f>SUMIFS('预算明细'!$J$6:$J$53,'预算明细'!$F$6:$F$53,$A8)</x:f>
         <x:v>26340</x:v>
       </x:c>
       <x:c r="E8" s="8" t="n">
@@ -536,15 +538,15 @@
         <x:v>3 入住后补</x:v>
       </x:c>
       <x:c r="B9" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$H$6:$H$51,'预算明细'!$F$6:$F$51,$A9)</x:f>
+        <x:f>SUMIFS('预算明细'!$H$6:$H$53,'预算明细'!$F$6:$F$53,$A9)</x:f>
         <x:v>11500</x:v>
       </x:c>
       <x:c r="C9" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$I$6:$I$51,'预算明细'!$F$6:$F$51,$A9)</x:f>
+        <x:f>SUMIFS('预算明细'!$I$6:$I$53,'预算明细'!$F$6:$F$53,$A9)</x:f>
         <x:v>18300</x:v>
       </x:c>
       <x:c r="D9" s="8" t="n">
-        <x:f>SUMIFS('预算明细'!$J$6:$J$51,'预算明细'!$F$6:$F$51,$A9)</x:f>
+        <x:f>SUMIFS('预算明细'!$J$6:$J$53,'预算明细'!$F$6:$F$53,$A9)</x:f>
         <x:v>14000</x:v>
       </x:c>
       <x:c r="E9" s="8" t="n">
@@ -587,15 +589,15 @@
       </x:c>
       <x:c r="B12" s="8" t="n">
         <x:f>SUM(B7:B8)</x:f>
-        <x:v>91700</x:v>
+        <x:v>92950</x:v>
       </x:c>
       <x:c r="C12" s="8" t="n">
         <x:f>SUM(C7:C8)</x:f>
-        <x:v>146700</x:v>
+        <x:v>149800</x:v>
       </x:c>
       <x:c r="D12" s="8" t="n">
         <x:f>SUM(D7:D8)</x:f>
-        <x:v>116000</x:v>
+        <x:v>117800</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
         <x:v>阶段一＋阶段二</x:v>
@@ -608,15 +610,15 @@
       </x:c>
       <x:c r="B13" s="8" t="n">
         <x:f>ROUNDUP(B12*$B$4/100,0)*100</x:f>
-        <x:v>9200</x:v>
+        <x:v>9300</x:v>
       </x:c>
       <x:c r="C13" s="8" t="n">
         <x:f>ROUNDUP(C12*$B$4/100,0)*100</x:f>
-        <x:v>14700</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D13" s="8" t="n">
         <x:f>ROUNDUP(D12*$B$4/100,0)*100</x:f>
-        <x:v>11600</x:v>
+        <x:v>11800</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
         <x:v>按入住前项目预留，
@@ -630,15 +632,15 @@
       </x:c>
       <x:c r="B14" s="18" t="n">
         <x:f>SUM(B12:B13)</x:f>
-        <x:v>100900</x:v>
+        <x:v>102250</x:v>
       </x:c>
       <x:c r="C14" s="18" t="n">
         <x:f>SUM(C12:C13)</x:f>
-        <x:v>161400</x:v>
+        <x:v>164800</x:v>
       </x:c>
       <x:c r="D14" s="18" t="n">
         <x:f>SUM(D12:D13)</x:f>
-        <x:v>127600</x:v>
+        <x:v>129600</x:v>
       </x:c>
       <x:c r="E14" s="19" t="str">
         <x:v>入住前准备资金</x:v>
@@ -672,15 +674,15 @@
       </x:c>
       <x:c r="B16" s="21" t="n">
         <x:f>SUM(B14:B15)</x:f>
-        <x:v>112400</x:v>
+        <x:v>113750</x:v>
       </x:c>
       <x:c r="C16" s="21" t="n">
         <x:f>SUM(C14:C15)</x:f>
-        <x:v>179700</x:v>
+        <x:v>183100</x:v>
       </x:c>
       <x:c r="D16" s="23" t="n">
         <x:f>SUM(D14:D15)</x:f>
-        <x:v>141600</x:v>
+        <x:v>143600</x:v>
       </x:c>
       <x:c r="E16" s="22" t="str">
         <x:v>应急金只计算一次</x:v>
@@ -836,9 +838,9 @@
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2"/>
     </x:row>
-    <x:row r="26" ht="25" customHeight="1">
-      <x:c r="A26" s="2" t="str">
-        <x:v>电脑硬件不计。扩充吊柜5500元未计；决定做后在明细把纳入改为1。</x:v>
+    <x:row r="26" ht="44" customHeight="1">
+      <x:c r="A26" s="29" t="str">
+        <x:v>两门上透气柜900元已计；八处扩充吊柜5500元可选未计。接口增量900元若全包已含，在明细纳入改0。</x:v>
       </x:c>
       <x:c r="B26" s="2"/>
       <x:c r="C26" s="2"/>
@@ -1460,8 +1462,7 @@
         <x:v>灯具与插排</x:v>
       </x:c>
       <x:c r="C44" s="13" t="str">
-        <x:v>模型补灯具、插座、开关、网口、两工位插排、插头和离地走线；16处灯具、37个电源插座
-。</x:v>
+        <x:v>模型有16灯、39电源面板、7开关组、5网口组（16端口）；工位插排、插头和离地走线。</x:v>
       </x:c>
       <x:c r="D44" s="13" t="str">
         <x:v>用户要求；数量为规划</x:v>
@@ -1517,17 +1518,53 @@
         <x:v>提前决策</x:v>
       </x:c>
       <x:c r="C48" s="13" t="str">
-        <x:v>水电、地面标高、蹲便、防水、设备柜位、柜体固定、门窗及进场验收等21项提前核对。</x:v>
+        <x:v>水电、地面标高、蹲便、防水、设备柜、悬挂固定、门窗等23项前置；新增洗漱外置和门外透气设备柜。</x:v>
       </x:c>
       <x:c r="D48" s="13" t="str">
         <x:v>本次用户要求</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="25" customHeight="1">
-      <x:c r="A49" s="2"/>
-      <x:c r="B49" s="2"/>
-      <x:c r="C49" s="2"/>
-      <x:c r="D49" s="2"/>
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
+      <x:c r="A49" s="13" t="str">
+        <x:v>卫生间</x:v>
+      </x:c>
+      <x:c r="B49" s="13" t="str">
+        <x:v>洗漱位置</x:v>
+      </x:c>
+      <x:c r="C49" s="13" t="str">
+        <x:v>洗漱台与蹲便站立区分开；默认门外洗漱，备选室内南墙侧放且门改外侧移门。</x:v>
+      </x:c>
+      <x:c r="D49" s="13" t="str">
+        <x:v>用户要求分开；两方案为助手建议</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
+      <x:c r="A50" s="13" t="str">
+        <x:v>门外上方</x:v>
+      </x:c>
+      <x:c r="B50" s="13" t="str">
+        <x:v>两个透气设备柜</x:v>
+      </x:c>
+      <x:c r="C50" s="13" t="str">
+        <x:v>卫生间入口门外上方做两独立透气柜，放语音音箱和Wi-Fi；55×30×40cm、底220cm为初步占位。</x:v>
+      </x:c>
+      <x:c r="D50" s="13" t="str">
+        <x:v>功能为用户确认；尺寸待实测</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
+      <x:c r="A51" s="13" t="str">
+        <x:v>模型</x:v>
+      </x:c>
+      <x:c r="B51" s="13" t="str">
+        <x:v>完整墙与半墙</x:v>
+      </x:c>
+      <x:c r="C51" s="13" t="str">
+        <x:v>完整2.7m墙体、半墙0.8m和隐藏三个视图保留；补齐门洞上方墙体。</x:v>
+      </x:c>
+      <x:c r="D51" s="13" t="str">
+        <x:v>用户要求</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1744,13 +1781,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L7" s="13" t="str">
-        <x:v>灯具线路、37个电源插座、7组开关、4组网口，窗边两工位
-；空调、窗帘、洗烘机、洗碗机及机器人接口。 梳妆接口移
-次卧，机器人及洗碗机水电移厨房相邻检修柜。</x:v>
+        <x:v>39个电源面板、7组开关、5组网口（16端口）；窗边双工位；门外洗漱台冷热
+水与排水，门外上方音箱、Wi-Fi两柜供电及双网线。</x:v>
       </x:c>
       <x:c r="M7" s="13" t="str">
-        <x:v>列完整点位图、回路、管线规格；此行含管线底盒，面板在灯具项。
-点位为规划，电工现场核定；不要把插排算作固定插座替代。</x:v>
+        <x:v>列完整点位图、回路、管线规格；此行含管线底盒，面板在灯具项。点位为规
+划，电工现场核定；不要把插排算作固定插座替代。 新增洗漱外置和两设备
+柜接口先另留900元增量，若公司水电套餐已包全则把增量行纳入改0，避免重
+复。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="92" customHeight="1">
@@ -2069,12 +2107,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L14" s="13" t="str">
-        <x:v>蹲便器及水箱、花洒、洗手盆/小浴室柜、地漏和基础配件；
-开放式淋浴。</x:v>
+        <x:v>蹲便、水箱、花洒、地漏；默认门外70×45cm悬空洗漱柜、盆、镜；备选室内
+南墙55×40cm柜并改外侧移门。</x:v>
       </x:c>
       <x:c r="M14" s="13" t="str">
-        <x:v>蹲便形式保留；便器设备按新购预留，旧件是否能复用现场核对。防
-水和管线在对应工种项。</x:v>
+        <x:v>蹲便形式保留；便器设备按新购预留，旧件是否能复用现场核对。防水和管线
+在对应工种项。 卫浴3500元含洗漱柜盆镜一次；两方案互斥，不买两套。门
+外溅水区基层与排水另核。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="92" customHeight="1">
@@ -2302,12 +2341,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L19" s="13" t="str">
-        <x:v>14处固定灯具，37个电源插座、7组开关、4组网口面板。两
-盏工位台灯在入住阶段另列。</x:v>
+        <x:v>14处固定灯具，原37电源、7开关、4网口面板；新增2电源和1网口面板计接口
+增量行。镜前灯随洗漱位置切换。</x:v>
       </x:c>
       <x:c r="M19" s="13" t="str">
-        <x:v>灯具包含适配湿区及安装配件；普通面板如水电套餐已含则扣重，智
-能件只另计升级差价。灯具数量不等于照度设计已完成。</x:v>
+        <x:v>灯具包含适配湿区及安装配件；普通面板如水电套餐已含则扣重，智能件只另
+计升级差价。灯具数量不等于照度设计已完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="92" customHeight="1">
@@ -2440,12 +2479,12 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L22" s="13" t="str">
-        <x:v>米家方向；手机、语音控制，基础音箱/网关/路由器和必要
-智能开关升级差价。</x:v>
+        <x:v>门外上方音箱仓和Wi-Fi仓：音箱250、路由器450、网关/智能开关差价500，
+共1200元；占位非选定机型。</x:v>
       </x:c>
       <x:c r="M22" s="13" t="str">
-        <x:v>型号应相互兼容，具体数量待点位图；普通面板已计价部分扣除，仅
-算升级差价。</x:v>
+        <x:v>设备只计在本行；柜体和接口在硬装。光猫与交换机是否由运营商提供及端口
+数量待确认，若需另购在报价中补齐。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="92" customHeight="1">
@@ -3792,48 +3831,118 @@
 空时选封底落地款。</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="25" customHeight="1">
-      <x:c r="A52" s="2"/>
-      <x:c r="B52" s="2"/>
-      <x:c r="C52" s="2"/>
-      <x:c r="D52" s="2"/>
-      <x:c r="E52" s="2"/>
-      <x:c r="F52" s="2"/>
-      <x:c r="G52" s="2"/>
-      <x:c r="H52" s="2"/>
-      <x:c r="I52" s="2"/>
-      <x:c r="J52" s="2"/>
-      <x:c r="K52" s="2"/>
-      <x:c r="L52" s="2"/>
-      <x:c r="M52" s="2"/>
-    </x:row>
-    <x:row r="53" ht="25" customHeight="1">
-      <x:c r="A53" s="2"/>
-      <x:c r="B53" s="2"/>
-      <x:c r="C53" s="2"/>
-      <x:c r="D53" s="2"/>
-      <x:c r="E53" s="2"/>
-      <x:c r="F53" s="2"/>
-      <x:c r="G53" s="2"/>
-      <x:c r="H53" s="2"/>
-      <x:c r="I53" s="2"/>
-      <x:c r="J53" s="2"/>
-      <x:c r="K53" s="2"/>
-      <x:c r="L53" s="2"/>
-      <x:c r="M53" s="2"/>
+    <x:row r="52" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A52" s="13" t="str">
+        <x:v>全包基础</x:v>
+      </x:c>
+      <x:c r="B52" s="13" t="str">
+        <x:v>卫生间门外双透气设备柜</x:v>
+      </x:c>
+      <x:c r="C52" s="27" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="D52" s="27" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="E52" s="27" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="F52" s="26" t="str">
+        <x:v>1 硬装施工</x:v>
+      </x:c>
+      <x:c r="G52" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H52" s="24" t="n">
+        <x:f>C52*G52</x:f>
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="I52" s="24" t="n">
+        <x:f>D52*G52</x:f>
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="J52" s="24" t="n">
+        <x:f>E52*G52</x:f>
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="K52" s="13" t="n">
+        <x:f>VALUE(LEFT(F52,1))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L52" s="13" t="str">
+        <x:v>两个独立55宽×30深×40高cm木质透气上柜，柜底220cm，柜顶260cm另10cm封顶
+；朝客厅开放，侧面格栅。</x:v>
+      </x:c>
+      <x:c r="M52" s="13" t="str">
+        <x:v>两柜各450元规划；非八处可选吊柜。按音箱拾音、路由器天线、插头弯曲和
+厂家散热要求复尺；核墙体固定、门头与检修。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A53" s="13" t="str">
+        <x:v>全包基础</x:v>
+      </x:c>
+      <x:c r="B53" s="13" t="str">
+        <x:v>洗漱外置与设备柜接口增量</x:v>
+      </x:c>
+      <x:c r="C53" s="27" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D53" s="27" t="n">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="E53" s="27" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="F53" s="26" t="str">
+        <x:v>1 硬装施工</x:v>
+      </x:c>
+      <x:c r="G53" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H53" s="24" t="n">
+        <x:f>C53*G53</x:f>
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="I53" s="24" t="n">
+        <x:f>D53*G53</x:f>
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="J53" s="24" t="n">
+        <x:f>E53*G53</x:f>
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="K53" s="13" t="n">
+        <x:f>VALUE(LEFT(F53,1))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L53" s="13" t="str">
+        <x:v>门外洗漱冷热水、带存水弯排水和局部防溅修复；两上柜独立电源D-P1/D-P2
+、N-D双网线至入户汇集及新增面板。</x:v>
+      </x:c>
+      <x:c r="M53" s="13" t="str">
+        <x:v>900元为未询价增量预留，已包进10500元全屋水电报价则纳入改0；不包含蹲
+便排污迁移或结构改动。选室内方案需重核门价与增量范围。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="F6:F51">
       <x:formula1>"1 硬装施工,2 入住必需,3 入住后补"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="G6:G51">
       <x:formula1>"0,1"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="F52:F53">
+      <x:formula1>"1 硬装施工,2 入住必需,3 入住后补"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G52:G53">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a5687cf531144fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b29603fb1af404c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3888,14 +3997,14 @@
       </x:c>
       <x:c r="B5" s="24" t="n">
         <x:f>'预算总览'!D7</x:f>
-        <x:v>89660</x:v>
+        <x:v>91460</x:v>
       </x:c>
       <x:c r="C5" s="24" t="n">
         <x:f>'预算总览'!E7</x:f>
-        <x:v>101260</x:v>
+        <x:v>103260</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>固定安装与预留接口完工验收。可选吊柜若做应此时施工。</x:v>
+        <x:v>固定安装验收，含门外洗漱管线及门上两透气柜；可选吊柜若做此时施工。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
@@ -3911,7 +4020,7 @@
         <x:v>26340</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
-        <x:v>硬装整改、设备调试后进场必要家具家电、窗帘与床品。</x:v>
+        <x:v>必要家具家电进场；音箱、路由器放开放仓，通电测温、唤醒和网络覆盖。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
@@ -4049,9 +4158,8 @@
         <x:v>水电重做及未来设备预留</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>灯具线路、37个电源插座、7组开关、4组网口，窗边两工位；空调、窗帘、洗烘机
-、洗碗机及机器人接口。 梳妆接口移次卧，机器人及洗碗机水电移厨房相邻检修柜
-。</x:v>
+        <x:v>39个电源面板、7组开关、5组网口（16端口）；窗边双工位；门外洗漱台冷热水与排水，门外上方音箱、Wi
+-Fi两柜供电及双网线。</x:v>
       </x:c>
       <x:c r="C6" s="24" t="n">
         <x:f>'预算明细'!E7</x:f>
@@ -4221,7 +4329,7 @@
         <x:v>基础卫浴</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
-        <x:v>蹲便器及水箱、花洒、洗手盆/小浴室柜、地漏和基础配件；开放式淋浴。</x:v>
+        <x:v>蹲便、水箱、花洒、地漏；默认门外70×45cm悬空洗漱柜、盆、镜；备选室内南墙55×40cm柜并改外侧移门。</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
         <x:f>'预算明细'!E14</x:f>
@@ -4342,8 +4450,8 @@
         <x:v>固定灯具与普通开关插座面板</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>14处固定灯具，37个电源插座、7组开关、4组网口面板。两盏工位台灯在入住阶段
-另列。</x:v>
+        <x:v>14处固定灯具，原37电源、7开关、4网口面板；新增2电源和1网口面板计接口增量行。镜前灯随洗漱位置切
+换。</x:v>
       </x:c>
       <x:c r="C18" s="24" t="n">
         <x:f>'预算明细'!E19</x:f>
@@ -4458,69 +4566,124 @@
         <x:v>待核</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="25" customHeight="1">
-      <x:c r="A23" s="2" t="str">
+    <x:row r="23" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A23" s="13" t="str">
+        <x:v>卫生间门外双透气设备柜</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>两个独立55宽×30深×40高cm木质透气上柜，柜底220cm，柜顶260cm另10cm封顶；朝客厅开放，侧面格栅。</x:v>
+      </x:c>
+      <x:c r="C23" s="24" t="n">
+        <x:f>'预算明细'!E52</x:f>
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="D23" s="27"/>
+      <x:c r="E23" s="24" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F23" s="27"/>
+      <x:c r="G23" s="24" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="H23" s="27"/>
+      <x:c r="I23" s="13" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A24" s="13" t="str">
+        <x:v>洗漱外置与设备柜接口增量</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="str">
+        <x:v>门外洗漱冷热水、带存水弯排水和局部防溅修复；两上柜独立电源D-P1/D-P2、N-D双网线至入户汇集及新增
+面板。</x:v>
+      </x:c>
+      <x:c r="C24" s="24" t="n">
+        <x:f>'预算明细'!E53</x:f>
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="D24" s="27"/>
+      <x:c r="E24" s="24" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F24" s="27"/>
+      <x:c r="G24" s="24" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="H24" s="27"/>
+      <x:c r="I24" s="13" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2" t="str">
         <x:v>额外服务费</x:v>
       </x:c>
-      <x:c r="B23" s="2" t="str">
+      <x:c r="B25" s="2" t="str">
         <x:v>管理、设计、运输等先核是否已包含，未含再填。</x:v>
       </x:c>
-      <x:c r="C23" s="8" t="n">
+      <x:c r="C25" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D23" s="11"/>
-      <x:c r="E23" s="8"/>
-      <x:c r="F23" s="11"/>
-      <x:c r="G23" s="8"/>
-      <x:c r="H23" s="11"/>
-      <x:c r="I23" s="2"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>必需范围合计</x:v>
-      </x:c>
-      <x:c r="C24" s="28" t="n">
-        <x:f>SUM(C5:C23)</x:f>
-        <x:v>89660</x:v>
-      </x:c>
-      <x:c r="D24" s="28" t="n">
-        <x:f>SUM(D5:D23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E24" s="28"/>
-      <x:c r="F24" s="28" t="n">
-        <x:f>SUM(F5:F23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="28"/>
-      <x:c r="H24" s="28" t="n">
-        <x:f>SUM(H5:H23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="C25" s="28"/>
-      <x:c r="D25" s="28"/>
-      <x:c r="E25" s="28"/>
-      <x:c r="F25" s="28"/>
-      <x:c r="G25" s="28"/>
-      <x:c r="H25" s="28"/>
+      <x:c r="D25" s="11"/>
+      <x:c r="E25" s="8"/>
+      <x:c r="F25" s="11"/>
+      <x:c r="G25" s="8"/>
+      <x:c r="H25" s="11"/>
+      <x:c r="I25" s="2"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
+        <x:v>必需范围合计</x:v>
+      </x:c>
+      <x:c r="B26"/>
+      <x:c r="C26" s="28" t="n">
+        <x:f>SUM(C5:C25)</x:f>
+        <x:v>91460</x:v>
+      </x:c>
+      <x:c r="D26" s="28" t="n">
+        <x:f>SUM(D5:D25)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="28"/>
+      <x:c r="F26" s="28" t="n">
+        <x:f>SUM(F5:F25)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="28"/>
+      <x:c r="H26" s="28" t="n">
+        <x:f>SUM(H5:H25)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27" s="28"/>
+      <x:c r="D27" s="28"/>
+      <x:c r="E27" s="28"/>
+      <x:c r="F27" s="28"/>
+      <x:c r="G27" s="28"/>
+      <x:c r="H27" s="28"/>
+      <x:c r="I27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
         <x:v>八处扩充吊柜另报价</x:v>
       </x:c>
-      <x:c r="B26" t="str">
+      <x:c r="B28" t="str">
         <x:v>可选，默认不计；基础柜顶和厨房标准吊柜已包含。</x:v>
       </x:c>
-      <x:c r="C26" s="28" t="n">
+      <x:c r="C28" s="28" t="n">
         <x:v>5500</x:v>
       </x:c>
-      <x:c r="D26" s="28"/>
-      <x:c r="E26" s="28"/>
-      <x:c r="F26" s="28"/>
-      <x:c r="G26" s="28"/>
-      <x:c r="H26" s="28"/>
+      <x:c r="D28" s="28"/>
+      <x:c r="E28" s="28"/>
+      <x:c r="F28" s="28"/>
+      <x:c r="G28" s="28"/>
+      <x:c r="H28" s="28"/>
+      <x:c r="I28"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4761,14 +4924,14 @@
         <x:v>主卧布局</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>1.8m宽、床长优先2.1m是助手建议；实测后用床架完整外尺寸排布，兼顾衣物区与梳妆台。</x:v>
+        <x:v>床宽1.8m、床长优先2.1m为方案建议；梳妆台在次卧，主卧衣物柜与床保留。</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
         <x:v>待实测与试躺</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
-        <x:v>本版默认床头靠图面右侧墙，180×210cm床垫的窄边床架脚边约63cm；可
-切回原朝向或比较200cm床长。</x:v>
+        <x:v>本版默认床头靠图面右侧墙，180×210cm床垫的窄边床架脚边约63cm；可切回原朝向或
+比较200cm床长。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="85" customHeight="1">
@@ -4776,8 +4939,7 @@
         <x:v>洗衣区与机器人</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>本版洗烘机在阳台右端、基站在卫生间外墙；实际型号未定，需复核排水进水、电源、开门
-与维修空间。</x:v>
+        <x:v>洗烘机仍在阳台右端；机器人基站已改厨房南短柜开放仓，门外墙段用于洗漱台与门上设备柜。</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>待现场定位</x:v>
@@ -4890,11 +5052,47 @@
 d589a1a516d35d85481d.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="25" customHeight="1">
-      <x:c r="A26" s="2"/>
-      <x:c r="B26" s="2"/>
-      <x:c r="C26" s="2"/>
-      <x:c r="D26" s="2"/>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="13" t="str">
+        <x:v>洗漱与便器使用空间</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="str">
+        <x:v>洗漱与蹲便站立区分开；洗漱台完成高先按85cm，中心与侧墙、便器前方空间按现场和所选设备复核。</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="str">
+        <x:v>JGJ 367-2015 4.7及条文说明；原则参考，非施工图</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="str">
+        <x:v>https://gf.cabr-fire.com/m/article-63613.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A27" s="13" t="str">
+        <x:v>路由器柜放置依据</x:v>
+      </x:c>
+      <x:c r="B27" s="13" t="str">
+        <x:v>官方建议房屋中间较高、无遮挡处，避免封闭金属箱和被阻挡柜位。因此门外柜向客厅开放、非金属；现场测覆盖与温度。</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="str">
+        <x:v>小米官方FAQ；放置原则参考，未选BE3600</x:v>
+      </x:c>
+      <x:c r="D27" s="13" t="str">
+        <x:v>https://www.mi.com/hk/support/faq/details/KA-502848/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A28" s="13" t="str">
+        <x:v>音箱与设备柜</x:v>
+      </x:c>
+      <x:c r="B28" s="13" t="str">
+        <x:v>音箱正面朝客厅开放、侧面通风；柜尺寸是占位，不是任何音箱或路由器通用安装规格。需按所选型号试唤醒和核厂家间距。</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="str">
+        <x:v>助手设计判断；实机和安装要求待验证</x:v>
+      </x:c>
+      <x:c r="D28" s="13" t="str">
+        <x:v>https://github.com/Shengshenlan/zhuangxiu/blob/main/布局/卫生间方案与门上设备柜_20261007.md</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5008,11 +5206,12 @@
         <x:v>改管、防水前</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>蹲便器与洗手盆同属浴室，梳妆台在次卧。湿区人工清扫。</x:v>
+        <x:v>蹲便在右侧，洗漱默认门外；淋浴移左侧，不做隔断，湿区人工清扫
+。</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>核原排污口、存水弯、所选蹲便安装深度与楼板条件。必要局部抬高，不能随意切挖结构；定地漏
-、坡向和挡水措施。</x:v>
+        <x:v>核原排污口、存水弯、所选蹲便安装深度与楼板条件。必要局部抬高，不能随意切挖结构；定地漏、坡向和挡水措施。 图面
+蹲便中心至右墙约41cm，保持原排污位置需现场确认；不以模型自行改排污。</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
         <x:v>设备安装剖面、防水闭水与排水试验记录</x:v>
@@ -5170,11 +5369,12 @@
         <x:v>开槽、水电前</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
-        <x:v>37电源面板、7开关组；电脑插排固定离地。</x:v>
+        <x:v>39电源面板、7开关组；柜内D-P1/D-P2约234cm独立供电，插排固定
+离地。</x:v>
       </x:c>
       <x:c r="D15" s="13" t="str">
-        <x:v>电工按设备真实功率定回路、保护、线径和接地。床头、次卧镜台、两工位、厨电位置先随成品外
-尺寸校核；厨房大功率设备按安装要求接电。</x:v>
+        <x:v>电工按设备真实功率定回路、保护、线径和接地。床头、次卧镜台、两工位、厨电位置先随成品外尺寸校核；厨房大功率设备
+按安装要求接电。</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
         <x:v>点位回路表、隐蔽照片、检测记录</x:v>
@@ -5191,10 +5391,11 @@
         <x:v>弱电布线前</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
-        <x:v>两工位各2口，电视2口，入户4口。</x:v>
+        <x:v>两工位各2口，电视2口，设备柜N-D 2口，入户N-E 8口，共16端口。</x:v>
       </x:c>
       <x:c r="D16" s="13" t="str">
-        <x:v>光纤入户路线、路由器供电和通风，网线与可换线管、电视HDMI走线、线缆标识及连接测试。</x:v>
+        <x:v>入户保留光猫/交换汇集；两条Cat6在入户与门上路由器仓间接WAN/LAN，六条到双工位和电视；穿管、强弱电分路、线缆标签
+和有线测试。先核运营商与最终设备拓扑，不承诺单台Wi-Fi全屋无死角。</x:v>
       </x:c>
       <x:c r="E16" s="13" t="str">
         <x:v>弱电拓扑和端口表</x:v>
@@ -5271,11 +5472,12 @@
         <x:v>墙面封闭、柜体下单前</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
-        <x:v>八处扩充吊柜约7.96延米可选5500。电视柜底18cm、镜台底66cm。</x:v>
+        <x:v>八处扩充吊柜5500可选；门外两个透气设备柜900已纳入。悬空洗漱
+柜底22cm。</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>吊柜若要做应硬装期确定，不等后期随意加。核墙体、梁、可靠固定、柜门与空调窗扇，不能只固
-定在装饰吊顶；必要改封底落地。</x:v>
+        <x:v>吊柜若要做应硬装期确定，不等后期随意加。核墙体、梁、可靠固定、柜门与空调窗扇，不能只固定在装饰吊顶；必要改封底
+落地。</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
         <x:v>固定节点、柜门开启与设备检修图</x:v>
@@ -5386,13 +5588,51 @@
         <x:v>施工和安装对应项目，不另重复收费</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="25" customHeight="1">
-      <x:c r="A26" s="2"/>
-      <x:c r="B26" s="2"/>
-      <x:c r="C26" s="2"/>
-      <x:c r="D26" s="2"/>
-      <x:c r="E26" s="2"/>
-      <x:c r="F26" s="2"/>
+    <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A26" s="13" t="str">
+        <x:v>门外洗漱与门扇</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="str">
+        <x:v>改管、防水、订门前</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="str">
+        <x:v>默认70×45cm门外柜，台面约85cm、柜底22cm；台前留80cm站立目标
+。</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="str">
+        <x:v>量门外墙段、动线、冷热水与带存水弯排水坡度；局部防溅基层与边缘收口由现场设计。备用室内55×40cm柜须改外侧移门，
+核轨道、门头、私密和防溅；不得与内开门同装。</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="str">
+        <x:v>洗漱/门开启/站立区平面与给排水剖面，两人现场试站</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="str">
+        <x:v>柜盆镜在卫浴3500；接口增量900；门项4500重新核
+价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A27" s="13" t="str">
+        <x:v>两透气设备柜</x:v>
+      </x:c>
+      <x:c r="B27" s="13" t="str">
+        <x:v>选设备、水电、柜体下单前</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="str">
+        <x:v>门外干区两独立55×30×40cm柜，底220cm、顶260cm另10cm封板，朝客
+厅敞开。</x:v>
+      </x:c>
+      <x:c r="D27" s="13" t="str">
+        <x:v>内净约51.4×26.4×36.4cm；先核设备机身、天线展开、线缆弯曲与厂家散热间距。两侧通风、前方不遮拾音/天线；非金属结
+构。核墙体与门头可固定，插座可检修，装机后试唤醒、测信号和温度。</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="str">
+        <x:v>柜体剖面、设备尺寸/散热安装图、供电和网络拓扑、
+通电试机</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="str">
+        <x:v>双柜900；接口增量900；设备1200原预算一次计入</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
